--- a/photo_analyzer/analysis_report.xlsx
+++ b/photo_analyzer/analysis_report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB13"/>
+  <dimension ref="A1:BG13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,127 +446,282 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>top_means_R</t>
+          <t>top_left_means_R</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>top_means_G</t>
+          <t>top_left_means_G</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>top_means_B</t>
+          <t>top_left_means_B</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>top_stds_R</t>
+          <t>top_left_stds_R</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>top_stds_G</t>
+          <t>top_left_stds_G</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>top_stds_B</t>
+          <t>top_left_stds_B</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>top_dominant</t>
+          <t>top_left_dominant</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>top_imbalance</t>
+          <t>top_left_imbalance</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>top_mean_std</t>
+          <t>top_left_green_ratio</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>top_var</t>
+          <t>top_left_red_ratio</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>top_entropy</t>
+          <t>top_left_blue_ratio</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>bottom_means_R</t>
+          <t>top_left_mean_std</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>bottom_means_G</t>
+          <t>top_left_var</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>bottom_means_B</t>
+          <t>top_left_entropy</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>bottom_stds_R</t>
+          <t>top_right_means_R</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>bottom_stds_G</t>
+          <t>top_right_means_G</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>bottom_stds_B</t>
+          <t>top_right_means_B</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>bottom_dominant</t>
+          <t>top_right_stds_R</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>bottom_imbalance</t>
+          <t>top_right_stds_G</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>bottom_mean_std</t>
+          <t>top_right_stds_B</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>bottom_var</t>
+          <t>top_right_dominant</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>bottom_entropy</t>
+          <t>top_right_imbalance</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>bottom_green_ratio</t>
+          <t>top_right_green_ratio</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>quality_diff_ratio</t>
+          <t>top_right_red_ratio</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>brightness_diff</t>
+          <t>top_right_blue_ratio</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>top_right_mean_std</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>top_right_var</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>top_right_entropy</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>bottom_left_means_R</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>bottom_left_means_G</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>bottom_left_means_B</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>bottom_left_stds_R</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>bottom_left_stds_G</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>bottom_left_stds_B</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>bottom_left_dominant</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>bottom_left_imbalance</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>bottom_left_green_ratio</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>bottom_left_red_ratio</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>bottom_left_blue_ratio</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>bottom_left_mean_std</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>bottom_left_var</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>bottom_left_entropy</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>bottom_right_means_R</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>bottom_right_means_G</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>bottom_right_means_B</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>bottom_right_stds_R</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>bottom_right_stds_G</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>bottom_right_stds_B</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>bottom_right_dominant</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>bottom_right_imbalance</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>bottom_right_green_ratio</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>bottom_right_red_ratio</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>bottom_right_blue_ratio</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>bottom_right_mean_std</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>bottom_right_var</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>bottom_right_entropy</t>
         </is>
       </c>
     </row>
@@ -576,10 +731,8 @@
           <t>DJI_20260406134845_0018_D.JPG</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="B2" t="b">
+        <v>0</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -587,22 +740,22 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>115.867</v>
+        <v>116.081</v>
       </c>
       <c r="E2" t="n">
-        <v>112.471</v>
+        <v>115.653</v>
       </c>
       <c r="F2" t="n">
-        <v>98.586</v>
+        <v>94.907</v>
       </c>
       <c r="G2" t="n">
-        <v>26.009</v>
+        <v>31.025</v>
       </c>
       <c r="H2" t="n">
-        <v>20.367</v>
+        <v>23.649</v>
       </c>
       <c r="I2" t="n">
-        <v>27.092</v>
+        <v>32.778</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -610,60 +763,157 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0.549</v>
+        <v>0.551</v>
       </c>
       <c r="L2" t="n">
-        <v>24.489</v>
+        <v>1.096</v>
       </c>
       <c r="M2" t="n">
-        <v>132.541</v>
+        <v>1.103</v>
       </c>
       <c r="N2" t="n">
-        <v>6.57</v>
+        <v>0.819</v>
       </c>
       <c r="O2" t="n">
-        <v>119.255</v>
+        <v>29.151</v>
       </c>
       <c r="P2" t="n">
-        <v>120.175</v>
+        <v>171.667</v>
       </c>
       <c r="Q2" t="n">
-        <v>95.137</v>
+        <v>6.773</v>
       </c>
       <c r="R2" t="n">
-        <v>32.635</v>
+        <v>123.551</v>
       </c>
       <c r="S2" t="n">
-        <v>25.823</v>
+        <v>117.81</v>
       </c>
       <c r="T2" t="n">
-        <v>35.299</v>
-      </c>
-      <c r="U2" t="inlineStr">
+        <v>106.542</v>
+      </c>
+      <c r="U2" t="n">
+        <v>19.088</v>
+      </c>
+      <c r="V2" t="n">
+        <v>17.346</v>
+      </c>
+      <c r="W2" t="n">
+        <v>19.534</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.551</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1.024</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.101</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.883</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>18.656</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>137.538</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>6.236</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>106.728</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>113.287</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>78.212</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>34.42</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>28.161</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>35.879</v>
+      </c>
+      <c r="AL2" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="V2" t="n">
-        <v>0.5610000000000001</v>
-      </c>
-      <c r="W2" t="n">
-        <v>31.252</v>
-      </c>
-      <c r="X2" t="n">
-        <v>228.612</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>6.942</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1.121</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>-7.643</v>
+      <c r="AM2" t="n">
+        <v>0.613</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1.225</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1.115</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0.711</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>32.82</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>355.8</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>7.025</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>126.599</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>124.712</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>105.024</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>32.512</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>26.247</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>33.565</v>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="BA2" t="n">
+        <v>0.551</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>1.077</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>1.102</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>0.836</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>30.775</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>136.589</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>6.898</v>
       </c>
     </row>
     <row r="3">
@@ -672,10 +922,8 @@
           <t>DJI_20260406134848_0019_D.JPG</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="B3" t="b">
+        <v>1</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -683,22 +931,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>126.001</v>
+        <v>126.126</v>
       </c>
       <c r="E3" t="n">
-        <v>126.152</v>
+        <v>126.519</v>
       </c>
       <c r="F3" t="n">
-        <v>124.761</v>
+        <v>125.265</v>
       </c>
       <c r="G3" t="n">
-        <v>10.79</v>
+        <v>11.29</v>
       </c>
       <c r="H3" t="n">
-        <v>9.513</v>
+        <v>9.606</v>
       </c>
       <c r="I3" t="n">
-        <v>14.332</v>
+        <v>14.542</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -709,57 +957,154 @@
         <v>0.503</v>
       </c>
       <c r="L3" t="n">
-        <v>11.545</v>
+        <v>1.007</v>
       </c>
       <c r="M3" t="n">
-        <v>22.511</v>
+        <v>1.002</v>
       </c>
       <c r="N3" t="n">
-        <v>0.87</v>
+        <v>0.992</v>
       </c>
       <c r="O3" t="n">
-        <v>128</v>
+        <v>11.813</v>
       </c>
       <c r="P3" t="n">
-        <v>128</v>
+        <v>24.012</v>
       </c>
       <c r="Q3" t="n">
-        <v>128</v>
+        <v>0.602</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>127.477</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>127.264</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="inlineStr">
+        <v>126.85</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3.626</v>
+      </c>
+      <c r="V3" t="n">
+        <v>4.197</v>
+      </c>
+      <c r="W3" t="n">
+        <v>6.215</v>
+      </c>
+      <c r="X3" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="V3" t="n">
+      <c r="Y3" t="n">
+        <v>0.502</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1.001</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.003</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.996</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>4.679</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>3.011</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.473</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>128</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>128</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>128</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="AM3" t="n">
         <v>0.5</v>
       </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
+      <c r="AN3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS3" t="n">
         <v>-0</v>
       </c>
-      <c r="Z3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>22.511</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>-7.087</v>
+      <c r="AT3" t="n">
+        <v>128</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>128</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>128</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="BA3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="4">
@@ -768,10 +1113,8 @@
           <t>DJI_20260406134851_0020_D.JPG</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="B4" t="b">
+        <v>1</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -779,22 +1122,22 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>122.029</v>
+        <v>122.398</v>
       </c>
       <c r="E4" t="n">
-        <v>122.53</v>
+        <v>123.434</v>
       </c>
       <c r="F4" t="n">
-        <v>119.75</v>
+        <v>121.243</v>
       </c>
       <c r="G4" t="n">
-        <v>18.538</v>
+        <v>18.239</v>
       </c>
       <c r="H4" t="n">
-        <v>15.965</v>
+        <v>15.265</v>
       </c>
       <c r="I4" t="n">
-        <v>22.196</v>
+        <v>21.395</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -805,57 +1148,154 @@
         <v>0.507</v>
       </c>
       <c r="L4" t="n">
-        <v>18.9</v>
+        <v>1.013</v>
       </c>
       <c r="M4" t="n">
-        <v>26.544</v>
+        <v>1</v>
       </c>
       <c r="N4" t="n">
-        <v>1.678</v>
+        <v>0.986</v>
       </c>
       <c r="O4" t="n">
-        <v>128</v>
+        <v>18.3</v>
       </c>
       <c r="P4" t="n">
-        <v>128</v>
+        <v>20.117</v>
       </c>
       <c r="Q4" t="n">
-        <v>128</v>
+        <v>1.076</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>126.441</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>126.006</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="inlineStr">
+        <v>124.863</v>
+      </c>
+      <c r="U4" t="n">
+        <v>9.403</v>
+      </c>
+      <c r="V4" t="n">
+        <v>9.148</v>
+      </c>
+      <c r="W4" t="n">
+        <v>12.617</v>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="V4" t="n">
+      <c r="Y4" t="n">
+        <v>0.504</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.003</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.008</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.989</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>10.389</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>11.787</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.006</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>128</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>128</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>128</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="AM4" t="n">
         <v>0.5</v>
       </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
+      <c r="AN4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="n">
         <v>-0</v>
       </c>
-      <c r="Z4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>26.544</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>-19.692</v>
+      <c r="AT4" t="n">
+        <v>128</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>128</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>128</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="BA4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="5">
@@ -864,10 +1304,8 @@
           <t>DJI_20260406134854_0021_D.JPG</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="B5" t="b">
+        <v>1</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -875,22 +1313,22 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>117.682</v>
+        <v>119.572</v>
       </c>
       <c r="E5" t="n">
-        <v>119.816</v>
+        <v>122.236</v>
       </c>
       <c r="F5" t="n">
-        <v>112.013</v>
+        <v>116.218</v>
       </c>
       <c r="G5" t="n">
-        <v>24.815</v>
+        <v>20.464</v>
       </c>
       <c r="H5" t="n">
-        <v>19.433</v>
+        <v>15.947</v>
       </c>
       <c r="I5" t="n">
-        <v>29.341</v>
+        <v>26.197</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -898,60 +1336,157 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>0.522</v>
+        <v>0.518</v>
       </c>
       <c r="L5" t="n">
-        <v>24.53</v>
+        <v>1.037</v>
       </c>
       <c r="M5" t="n">
-        <v>71.062</v>
+        <v>1.003</v>
       </c>
       <c r="N5" t="n">
-        <v>3.016</v>
+        <v>0.961</v>
       </c>
       <c r="O5" t="n">
-        <v>128</v>
+        <v>20.869</v>
       </c>
       <c r="P5" t="n">
-        <v>128</v>
+        <v>55.915</v>
       </c>
       <c r="Q5" t="n">
-        <v>128</v>
+        <v>1.914</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>124.055</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>123.95</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="inlineStr">
+        <v>120.61</v>
+      </c>
+      <c r="U5" t="n">
+        <v>18.994</v>
+      </c>
+      <c r="V5" t="n">
+        <v>15.141</v>
+      </c>
+      <c r="W5" t="n">
+        <v>21.429</v>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="V5" t="n">
+      <c r="Y5" t="n">
+        <v>0.507</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.013</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.015</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.973</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>18.522</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>29.586</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.939</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>128</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>128</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>128</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="AM5" t="n">
         <v>0.5</v>
       </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
+      <c r="AN5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
         <v>-0</v>
       </c>
-      <c r="Z5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>71.062</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>-34.489</v>
+      <c r="AT5" t="n">
+        <v>128</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>128</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>128</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="BA5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="6">
@@ -960,10 +1495,8 @@
           <t>DJI_20260406134857_0022_D.JPG</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="B6" t="b">
+        <v>1</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -971,22 +1504,22 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>118.566</v>
+        <v>121.91</v>
       </c>
       <c r="E6" t="n">
-        <v>122.019</v>
+        <v>124.442</v>
       </c>
       <c r="F6" t="n">
-        <v>114.688</v>
+        <v>119.413</v>
       </c>
       <c r="G6" t="n">
-        <v>26.785</v>
+        <v>20.885</v>
       </c>
       <c r="H6" t="n">
-        <v>18.387</v>
+        <v>13.97</v>
       </c>
       <c r="I6" t="n">
-        <v>30.096</v>
+        <v>24.579</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -994,60 +1527,157 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>0.523</v>
+        <v>0.516</v>
       </c>
       <c r="L6" t="n">
-        <v>25.089</v>
+        <v>1.031</v>
       </c>
       <c r="M6" t="n">
-        <v>71.755</v>
+        <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>2.318</v>
+        <v>0.969</v>
       </c>
       <c r="O6" t="n">
-        <v>128</v>
+        <v>19.812</v>
       </c>
       <c r="P6" t="n">
-        <v>128</v>
+        <v>50.078</v>
       </c>
       <c r="Q6" t="n">
-        <v>128</v>
+        <v>1.5</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>122.776</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>124.386</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="inlineStr">
+        <v>120.623</v>
+      </c>
+      <c r="U6" t="n">
+        <v>21.599</v>
+      </c>
+      <c r="V6" t="n">
+        <v>15.081</v>
+      </c>
+      <c r="W6" t="n">
+        <v>23.799</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.511</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.022</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.002</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.976</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>20.159</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>36.239</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.475</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>128</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>128</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>128</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="V6" t="n">
+      <c r="AM6" t="n">
         <v>0.5</v>
       </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
+      <c r="AN6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
         <v>-0</v>
       </c>
-      <c r="Z6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>71.755</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>-28.727</v>
+      <c r="AT6" t="n">
+        <v>128</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>128</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>128</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="BA6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="7">
@@ -1056,10 +1686,8 @@
           <t>DJI_20260406134901_0023_D.JPG</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="B7" t="b">
+        <v>1</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1067,22 +1695,22 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>101.326</v>
+        <v>113.795</v>
       </c>
       <c r="E7" t="n">
-        <v>109.515</v>
+        <v>117.904</v>
       </c>
       <c r="F7" t="n">
-        <v>97.819</v>
+        <v>110.991</v>
       </c>
       <c r="G7" t="n">
-        <v>53.886</v>
+        <v>45.006</v>
       </c>
       <c r="H7" t="n">
-        <v>39.946</v>
+        <v>33.685</v>
       </c>
       <c r="I7" t="n">
-        <v>52.304</v>
+        <v>43.229</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1090,60 +1718,157 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>0.55</v>
+        <v>0.525</v>
       </c>
       <c r="L7" t="n">
-        <v>48.712</v>
+        <v>1.049</v>
       </c>
       <c r="M7" t="n">
-        <v>88.262</v>
+        <v>0.994</v>
       </c>
       <c r="N7" t="n">
-        <v>2.797</v>
+        <v>0.958</v>
       </c>
       <c r="O7" t="n">
-        <v>128</v>
+        <v>40.64</v>
       </c>
       <c r="P7" t="n">
-        <v>128</v>
+        <v>46.392</v>
       </c>
       <c r="Q7" t="n">
-        <v>128</v>
+        <v>1.903</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>110.218</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>115.929</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="inlineStr">
+        <v>108.817</v>
+      </c>
+      <c r="U7" t="n">
+        <v>42.329</v>
+      </c>
+      <c r="V7" t="n">
+        <v>30.676</v>
+      </c>
+      <c r="W7" t="n">
+        <v>42.976</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.529</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.059</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.981</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.962</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>38.66</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>59.734</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.732</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>128</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>128</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>128</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="V7" t="n">
+      <c r="AM7" t="n">
         <v>0.5</v>
       </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
+      <c r="AN7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
         <v>-0</v>
       </c>
-      <c r="Z7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>88.262</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>-75.339</v>
+      <c r="AT7" t="n">
+        <v>128</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>128</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>128</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="BA7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="8">
@@ -1152,10 +1877,8 @@
           <t>DJI_20260406134904_0024_D.JPG</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="B8" t="b">
+        <v>1</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1163,22 +1886,22 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>126.28</v>
+        <v>126.369</v>
       </c>
       <c r="E8" t="n">
-        <v>127.28</v>
+        <v>127.251</v>
       </c>
       <c r="F8" t="n">
-        <v>123.526</v>
+        <v>124.511</v>
       </c>
       <c r="G8" t="n">
-        <v>18.629</v>
+        <v>15.2</v>
       </c>
       <c r="H8" t="n">
-        <v>13.918</v>
+        <v>11.429</v>
       </c>
       <c r="I8" t="n">
-        <v>19.001</v>
+        <v>15.984</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1186,60 +1909,157 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>0.51</v>
+        <v>0.507</v>
       </c>
       <c r="L8" t="n">
-        <v>17.183</v>
+        <v>1.014</v>
       </c>
       <c r="M8" t="n">
-        <v>37.792</v>
+        <v>1.004</v>
       </c>
       <c r="N8" t="n">
-        <v>1.499</v>
+        <v>0.982</v>
       </c>
       <c r="O8" t="n">
-        <v>128</v>
+        <v>14.204</v>
       </c>
       <c r="P8" t="n">
-        <v>128</v>
+        <v>27.89</v>
       </c>
       <c r="Q8" t="n">
-        <v>128</v>
+        <v>0.991</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>127.569</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>127.886</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="inlineStr">
+        <v>126.124</v>
+      </c>
+      <c r="U8" t="n">
+        <v>13.632</v>
+      </c>
+      <c r="V8" t="n">
+        <v>10.086</v>
+      </c>
+      <c r="W8" t="n">
+        <v>13.63</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.504</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.008</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.004</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.987</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>12.45</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>17.574</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>128</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>128</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>128</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="V8" t="n">
+      <c r="AM8" t="n">
         <v>0.5</v>
       </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
+      <c r="AN8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
         <v>-0</v>
       </c>
-      <c r="Z8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>37.792</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>-6.913</v>
+      <c r="AT8" t="n">
+        <v>128</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>128</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>128</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="BA8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="9">
@@ -1248,10 +2068,8 @@
           <t>DJI_20260406134908_0025_D.JPG</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="B9" t="b">
+        <v>0</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1259,22 +2077,22 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>117.169</v>
+        <v>109.017</v>
       </c>
       <c r="E9" t="n">
-        <v>125.672</v>
+        <v>121.814</v>
       </c>
       <c r="F9" t="n">
-        <v>93.88</v>
+        <v>83.931</v>
       </c>
       <c r="G9" t="n">
-        <v>50.406</v>
+        <v>48.555</v>
       </c>
       <c r="H9" t="n">
-        <v>39.308</v>
+        <v>40.157</v>
       </c>
       <c r="I9" t="n">
-        <v>43.668</v>
+        <v>39.052</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1282,60 +2100,157 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>0.595</v>
+        <v>0.631</v>
       </c>
       <c r="L9" t="n">
-        <v>44.461</v>
+        <v>1.263</v>
       </c>
       <c r="M9" t="n">
-        <v>423.768</v>
+        <v>1.06</v>
       </c>
       <c r="N9" t="n">
-        <v>7.444</v>
+        <v>0.727</v>
       </c>
       <c r="O9" t="n">
-        <v>124.168</v>
+        <v>42.588</v>
       </c>
       <c r="P9" t="n">
-        <v>134.143</v>
+        <v>620.151</v>
       </c>
       <c r="Q9" t="n">
-        <v>96.345</v>
+        <v>7.315</v>
       </c>
       <c r="R9" t="n">
-        <v>52.359</v>
+        <v>132.633</v>
       </c>
       <c r="S9" t="n">
-        <v>40.599</v>
+        <v>136.04</v>
       </c>
       <c r="T9" t="n">
-        <v>47.255</v>
-      </c>
-      <c r="U9" t="inlineStr">
+        <v>107.792</v>
+      </c>
+      <c r="U9" t="n">
+        <v>51.106</v>
+      </c>
+      <c r="V9" t="n">
+        <v>38.355</v>
+      </c>
+      <c r="W9" t="n">
+        <v>47.487</v>
+      </c>
+      <c r="X9" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="V9" t="n">
-        <v>0.608</v>
-      </c>
-      <c r="W9" t="n">
-        <v>46.737</v>
-      </c>
-      <c r="X9" t="n">
-        <v>568.639</v>
-      </c>
       <c r="Y9" t="n">
-        <v>7.497</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.217</v>
+        <v>1.132</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.745</v>
+        <v>1.088</v>
       </c>
       <c r="AB9" t="n">
-        <v>-17.934</v>
+        <v>0.802</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>45.649</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>413.589</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>7.346</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>109.962</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>125.55</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>80.771</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>50.019</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>40.593</v>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="AM9" t="n">
+        <v>0.658</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1.317</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1.066</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0.6860000000000001</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>44.071</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>754.211</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>7.401</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>136.668</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>143.008</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>109.931</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>51.51</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>37.857</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>49.072</v>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="BA9" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>1.081</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0.786</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>46.147</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>317.733</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>7.26</v>
       </c>
     </row>
     <row r="10">
@@ -1353,22 +2268,22 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>48.623</v>
+        <v>31.213</v>
       </c>
       <c r="E10" t="n">
-        <v>65.726</v>
+        <v>53.255</v>
       </c>
       <c r="F10" t="n">
-        <v>35.771</v>
+        <v>22.408</v>
       </c>
       <c r="G10" t="n">
-        <v>63.437</v>
+        <v>58.037</v>
       </c>
       <c r="H10" t="n">
-        <v>41.261</v>
+        <v>37.763</v>
       </c>
       <c r="I10" t="n">
-        <v>46.479</v>
+        <v>41.378</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1376,60 +2291,157 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>0.779</v>
+        <v>0.993</v>
       </c>
       <c r="L10" t="n">
-        <v>50.392</v>
+        <v>1.986</v>
       </c>
       <c r="M10" t="n">
-        <v>62.115</v>
+        <v>0.825</v>
       </c>
       <c r="N10" t="n">
-        <v>4.626</v>
+        <v>0.531</v>
       </c>
       <c r="O10" t="n">
-        <v>0.093</v>
+        <v>45.726</v>
       </c>
       <c r="P10" t="n">
-        <v>33.862</v>
+        <v>42.939</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.195</v>
+        <v>4.161</v>
       </c>
       <c r="R10" t="n">
-        <v>1.275</v>
+        <v>27.192</v>
       </c>
       <c r="S10" t="n">
-        <v>5.748</v>
+        <v>52.583</v>
       </c>
       <c r="T10" t="n">
-        <v>2.262</v>
-      </c>
-      <c r="U10" t="inlineStr">
+        <v>20.6</v>
+      </c>
+      <c r="U10" t="n">
+        <v>50.801</v>
+      </c>
+      <c r="V10" t="n">
+        <v>33.561</v>
+      </c>
+      <c r="W10" t="n">
+        <v>38.577</v>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="V10" t="n">
-        <v>117.81</v>
-      </c>
-      <c r="W10" t="n">
-        <v>3.095</v>
-      </c>
-      <c r="X10" t="n">
-        <v>3.66</v>
-      </c>
       <c r="Y10" t="n">
-        <v>2.511</v>
+        <v>1.1</v>
       </c>
       <c r="Z10" t="n">
-        <v>235.62</v>
+        <v>2.201</v>
       </c>
       <c r="AA10" t="n">
-        <v>16.972</v>
+        <v>0.743</v>
       </c>
       <c r="AB10" t="n">
-        <v>115.971</v>
+        <v>0.516</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>40.979</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>35.757</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>3.297</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>32.345</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0.419</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>4.194</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0.628</v>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="AM10" t="n">
+        <v>737.229</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1474.457</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.747</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>2.287</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>2.218</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0.153</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>35.475</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0.399</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.613</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>7.087</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>3.476</v>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="BA10" t="n">
+        <v>64.246</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>128.491</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>4.059</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>5.528</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>2.473</v>
       </c>
     </row>
     <row r="11">
@@ -1438,10 +2450,8 @@
           <t>DJI_20260406140559_0002_D.JPG</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="B11" t="b">
+        <v>0</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1449,22 +2459,22 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>137.448</v>
+        <v>147.25</v>
       </c>
       <c r="E11" t="n">
-        <v>126.775</v>
+        <v>132.175</v>
       </c>
       <c r="F11" t="n">
-        <v>105.727</v>
+        <v>107.642</v>
       </c>
       <c r="G11" t="n">
-        <v>23.643</v>
+        <v>27.545</v>
       </c>
       <c r="H11" t="n">
-        <v>16.636</v>
+        <v>18.577</v>
       </c>
       <c r="I11" t="n">
-        <v>16.254</v>
+        <v>18.293</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1472,60 +2482,157 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>0.591</v>
+        <v>0.614</v>
       </c>
       <c r="L11" t="n">
-        <v>18.844</v>
+        <v>1.037</v>
       </c>
       <c r="M11" t="n">
-        <v>110.573</v>
+        <v>1.228</v>
       </c>
       <c r="N11" t="n">
-        <v>6.147</v>
+        <v>0.77</v>
       </c>
       <c r="O11" t="n">
-        <v>147.664</v>
+        <v>21.472</v>
       </c>
       <c r="P11" t="n">
-        <v>135.052</v>
+        <v>108.789</v>
       </c>
       <c r="Q11" t="n">
-        <v>109.013</v>
+        <v>6.36</v>
       </c>
       <c r="R11" t="n">
-        <v>24.625</v>
+        <v>130.906</v>
       </c>
       <c r="S11" t="n">
-        <v>16.689</v>
+        <v>124.395</v>
       </c>
       <c r="T11" t="n">
-        <v>17.985</v>
-      </c>
-      <c r="U11" t="inlineStr">
+        <v>103.397</v>
+      </c>
+      <c r="U11" t="n">
+        <v>17.008</v>
+      </c>
+      <c r="V11" t="n">
+        <v>14.456</v>
+      </c>
+      <c r="W11" t="n">
+        <v>15.536</v>
+      </c>
+      <c r="X11" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="V11" t="n">
-        <v>0.605</v>
-      </c>
-      <c r="W11" t="n">
-        <v>19.766</v>
-      </c>
-      <c r="X11" t="n">
-        <v>127.061</v>
-      </c>
       <c r="Y11" t="n">
-        <v>6.268</v>
+        <v>0.575</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.052</v>
+        <v>1.062</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.87</v>
+        <v>1.149</v>
       </c>
       <c r="AB11" t="n">
-        <v>-21.779</v>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>15.667</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>141.91</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>5.983</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>156.489</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>138.303</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>110.859</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>24.002</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>15.651</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>18.489</v>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="AM11" t="n">
+        <v>0.628</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1.035</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1.256</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0.752</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>19.381</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>118.556</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>6.201</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>143.76</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>135.407</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>110.214</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>22.262</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>16.205</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>16.721</v>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="BA11" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>1.066</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>1.171</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>18.396</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>120.906</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>6.138</v>
       </c>
     </row>
     <row r="12">
@@ -1534,10 +2641,8 @@
           <t>DJI_20260406140603_0003_D.JPG</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="B12" t="b">
+        <v>0</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1545,22 +2650,22 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>134.471</v>
+        <v>142.14</v>
       </c>
       <c r="E12" t="n">
-        <v>123.952</v>
+        <v>128.108</v>
       </c>
       <c r="F12" t="n">
-        <v>104.631</v>
+        <v>105.668</v>
       </c>
       <c r="G12" t="n">
-        <v>20.803</v>
+        <v>25.716</v>
       </c>
       <c r="H12" t="n">
-        <v>15.137</v>
+        <v>17.718</v>
       </c>
       <c r="I12" t="n">
-        <v>15.125</v>
+        <v>17.086</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1568,60 +2673,157 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>0.588</v>
+        <v>0.608</v>
       </c>
       <c r="L12" t="n">
-        <v>17.022</v>
+        <v>1.034</v>
       </c>
       <c r="M12" t="n">
-        <v>108.927</v>
+        <v>1.216</v>
       </c>
       <c r="N12" t="n">
-        <v>5.994</v>
+        <v>0.782</v>
       </c>
       <c r="O12" t="n">
-        <v>142.912</v>
+        <v>20.173</v>
       </c>
       <c r="P12" t="n">
-        <v>132.271</v>
+        <v>108.966</v>
       </c>
       <c r="Q12" t="n">
-        <v>106.764</v>
+        <v>6.229</v>
       </c>
       <c r="R12" t="n">
-        <v>24.748</v>
+        <v>130.249</v>
       </c>
       <c r="S12" t="n">
-        <v>17.052</v>
+        <v>123.105</v>
       </c>
       <c r="T12" t="n">
-        <v>17.919</v>
-      </c>
-      <c r="U12" t="inlineStr">
+        <v>103.641</v>
+      </c>
+      <c r="U12" t="n">
+        <v>16.295</v>
+      </c>
+      <c r="V12" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="W12" t="n">
+        <v>14.916</v>
+      </c>
+      <c r="X12" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="V12" t="n">
-        <v>0.598</v>
-      </c>
-      <c r="W12" t="n">
-        <v>19.906</v>
-      </c>
-      <c r="X12" t="n">
-        <v>122.859</v>
-      </c>
       <c r="Y12" t="n">
-        <v>6.285</v>
+        <v>0.574</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.06</v>
+        <v>1.053</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.887</v>
+        <v>1.149</v>
       </c>
       <c r="AB12" t="n">
-        <v>-18.893</v>
+        <v>0.8179999999999999</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>14.97</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>132.55</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>5.922</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>153.587</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>137.676</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>110.09</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>26.59</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>17.202</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>19.34</v>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="AM12" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1.044</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0.756</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>21.044</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>115.565</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>6.335</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>135.55</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>130.22</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>105.098</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>18.891</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>15.486</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>16.304</v>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="BA12" t="n">
+        <v>0.576</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1.082</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>1.152</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>16.894</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>119.369</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>6.066</v>
       </c>
     </row>
     <row r="13">
@@ -1630,10 +2832,8 @@
           <t>DJI_20260406140603_0004_D.JPG</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="B13" t="b">
+        <v>1</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1673,17 +2873,17 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>-0</v>
       </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
@@ -1693,31 +2893,128 @@
       <c r="T13" t="n">
         <v>0</v>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
       <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
         <v>-0</v>
       </c>
-      <c r="Z13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0</v>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>-0</v>
       </c>
     </row>
   </sheetData>

--- a/photo_analyzer/analysis_report.xlsx
+++ b/photo_analyzer/analysis_report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG13"/>
+  <dimension ref="A1:BU14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -724,6 +724,76 @@
           <t>bottom_right_entropy</t>
         </is>
       </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>overall_means_R</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>overall_means_G</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>overall_means_B</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>overall_stds_R</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>overall_stds_G</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>overall_stds_B</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>overall_dominant</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>overall_imbalance</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>overall_green_ratio</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>overall_red_ratio</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>overall_blue_ratio</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>overall_mean_std</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>overall_var</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>overall_entropy</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -915,6 +985,50 @@
       <c r="BG2" t="n">
         <v>6.898</v>
       </c>
+      <c r="BH2" t="n">
+        <v>118.239</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>117.866</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>96.17100000000001</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>30.838</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>24.571</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>33.091</v>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="BO2" t="n">
+        <v>0.552</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>1.099</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>1.105</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>200.203</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>6.859</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1106,6 +1220,50 @@
       <c r="BG3" t="n">
         <v>-0</v>
       </c>
+      <c r="BH3" t="n">
+        <v>127.401</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>127.446</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>127.029</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>5.979</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>5.277</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>7.986</v>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="BO3" t="n">
+        <v>0.501</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>1.002</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>1.001</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>0.997</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>6.414</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>6.755</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>0.3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1297,6 +1455,50 @@
       <c r="BG4" t="n">
         <v>-0</v>
       </c>
+      <c r="BH4" t="n">
+        <v>126.21</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>126.36</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>125.527</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>10.513</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>9.093</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>12.727</v>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="BO4" t="n">
+        <v>0.502</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>1.004</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>1.002</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>0.994</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>10.778</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>7.974</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>0.589</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1488,6 +1690,50 @@
       <c r="BG5" t="n">
         <v>-0</v>
       </c>
+      <c r="BH5" t="n">
+        <v>124.907</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>125.546</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>123.207</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>14.386</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>11.282</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>17.657</v>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="BO5" t="n">
+        <v>0.506</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>1.012</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>1.004</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>0.984</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>14.442</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>21.358</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>1.082</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1679,6 +1925,50 @@
       <c r="BG6" t="n">
         <v>-0</v>
       </c>
+      <c r="BH6" t="n">
+        <v>125.172</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>126.207</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>124.009</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>15.29</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>10.434</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>17.571</v>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="BO6" t="n">
+        <v>0.506</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>1.013</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>1.001</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>0.987</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>14.431</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>21.566</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>0.819</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1870,6 +2160,50 @@
       <c r="BG7" t="n">
         <v>-0</v>
       </c>
+      <c r="BH7" t="n">
+        <v>120.003</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>122.458</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>118.952</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>31.935</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>23.455</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>31.802</v>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="BO7" t="n">
+        <v>0.512</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>1.025</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>0.994</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>0.981</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>29.064</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>26.518</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>1.029</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2061,6 +2395,50 @@
       <c r="BG8" t="n">
         <v>-0</v>
       </c>
+      <c r="BH8" t="n">
+        <v>127.484</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>127.784</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>126.659</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>10.23</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>7.628</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>10.604</v>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="BO8" t="n">
+        <v>0.503</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>1.006</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>1.002</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>0.992</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>9.487</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>11.355</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>0.519</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2252,6 +2630,50 @@
       <c r="BG9" t="n">
         <v>7.26</v>
       </c>
+      <c r="BH9" t="n">
+        <v>122.07</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>131.603</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>95.60599999999999</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>51.88</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>40.403</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>46.222</v>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="BO9" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>1.209</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>1.075</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>0.754</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>46.169</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>525.857</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>7.487</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2443,6 +2865,50 @@
       <c r="BG10" t="n">
         <v>2.473</v>
       </c>
+      <c r="BH10" t="n">
+        <v>14.642</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>43.415</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>10.86</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>41.255</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>27.325</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>30.281</v>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="BO10" t="n">
+        <v>1.702</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>3.405</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>32.954</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>21.619</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>3.388</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2634,6 +3100,50 @@
       <c r="BG11" t="n">
         <v>6.138</v>
       </c>
+      <c r="BH11" t="n">
+        <v>144.601</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>132.57</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>108.028</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>24.781</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>17.099</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>17.549</v>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="BO11" t="n">
+        <v>0.601</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>1.202</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>19.809</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>122.402</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>6.269</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2825,6 +3335,50 @@
       <c r="BG12" t="n">
         <v>6.066</v>
       </c>
+      <c r="BH12" t="n">
+        <v>140.382</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>129.777</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>106.124</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>23.949</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>16.935</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>17.157</v>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="BO12" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>1.053</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>0.786</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>19.347</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>118.963</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>6.232</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3015,6 +3569,285 @@
       </c>
       <c r="BG13" t="n">
         <v>-0</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN13" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="BO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>IX-12-12730_0496_0009.JPG</t>
+        </is>
+      </c>
+      <c r="B14" t="b">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>5472x3648</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>85.84399999999999</v>
+      </c>
+      <c r="E14" t="n">
+        <v>182.645</v>
+      </c>
+      <c r="F14" t="n">
+        <v>48.915</v>
+      </c>
+      <c r="G14" t="n">
+        <v>63.727</v>
+      </c>
+      <c r="H14" t="n">
+        <v>51.262</v>
+      </c>
+      <c r="I14" t="n">
+        <v>45.429</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>1.355</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2.711</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.741</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="O14" t="n">
+        <v>53.473</v>
+      </c>
+      <c r="P14" t="n">
+        <v>8759.894</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>4.316</v>
+      </c>
+      <c r="R14" t="n">
+        <v>70.836</v>
+      </c>
+      <c r="S14" t="n">
+        <v>176.154</v>
+      </c>
+      <c r="T14" t="n">
+        <v>35.308</v>
+      </c>
+      <c r="U14" t="n">
+        <v>44.647</v>
+      </c>
+      <c r="V14" t="n">
+        <v>54.111</v>
+      </c>
+      <c r="W14" t="n">
+        <v>26.501</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.319</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>41.753</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>8449.906999999999</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>143.664</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>154.577</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>92.747</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>42.064</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>19.571</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>34.653</v>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="AM14" t="n">
+        <v>0.654</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1.308</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1.162</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0.622</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>32.096</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>75.923</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>6.528</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>137.428</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>57.253</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>14.993</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>15.501</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="BA14" t="n">
+        <v>0.855</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>1.063</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>0.475</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>14.531</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>82.16</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>5.861</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>100.961</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>162.701</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>58.556</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>52.475</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>43.193</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>38.544</v>
+      </c>
+      <c r="BN14" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="BO14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>0.913</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>44.738</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>4340.768</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>5.749</v>
       </c>
     </row>
   </sheetData>

--- a/photo_analyzer/analysis_report.xlsx
+++ b/photo_analyzer/analysis_report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BU14"/>
+  <dimension ref="A1:BT14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,355 +441,350 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>size</t>
+          <t>top_left_means_R</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>top_left_means_R</t>
+          <t>top_left_means_G</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>top_left_means_G</t>
+          <t>top_left_means_B</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>top_left_means_B</t>
+          <t>top_left_stds_R</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>top_left_stds_R</t>
+          <t>top_left_stds_G</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>top_left_stds_G</t>
+          <t>top_left_stds_B</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>top_left_stds_B</t>
+          <t>top_left_dominant</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>top_left_dominant</t>
+          <t>top_left_imbalance</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>top_left_imbalance</t>
+          <t>top_left_green_ratio</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>top_left_green_ratio</t>
+          <t>top_left_red_ratio</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>top_left_red_ratio</t>
+          <t>top_left_blue_ratio</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>top_left_blue_ratio</t>
+          <t>top_left_mean_std</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>top_left_mean_std</t>
+          <t>top_left_var</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>top_left_var</t>
+          <t>top_left_entropy</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>top_left_entropy</t>
+          <t>top_right_means_R</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>top_right_means_R</t>
+          <t>top_right_means_G</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>top_right_means_G</t>
+          <t>top_right_means_B</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>top_right_means_B</t>
+          <t>top_right_stds_R</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>top_right_stds_R</t>
+          <t>top_right_stds_G</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>top_right_stds_G</t>
+          <t>top_right_stds_B</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>top_right_stds_B</t>
+          <t>top_right_dominant</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>top_right_dominant</t>
+          <t>top_right_imbalance</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>top_right_imbalance</t>
+          <t>top_right_green_ratio</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>top_right_green_ratio</t>
+          <t>top_right_red_ratio</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>top_right_red_ratio</t>
+          <t>top_right_blue_ratio</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>top_right_blue_ratio</t>
+          <t>top_right_mean_std</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>top_right_mean_std</t>
+          <t>top_right_var</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>top_right_var</t>
+          <t>top_right_entropy</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>top_right_entropy</t>
+          <t>bottom_left_means_R</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>bottom_left_means_R</t>
+          <t>bottom_left_means_G</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>bottom_left_means_G</t>
+          <t>bottom_left_means_B</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>bottom_left_means_B</t>
+          <t>bottom_left_stds_R</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>bottom_left_stds_R</t>
+          <t>bottom_left_stds_G</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>bottom_left_stds_G</t>
+          <t>bottom_left_stds_B</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>bottom_left_stds_B</t>
+          <t>bottom_left_dominant</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>bottom_left_dominant</t>
+          <t>bottom_left_imbalance</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>bottom_left_imbalance</t>
+          <t>bottom_left_green_ratio</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>bottom_left_green_ratio</t>
+          <t>bottom_left_red_ratio</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>bottom_left_red_ratio</t>
+          <t>bottom_left_blue_ratio</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>bottom_left_blue_ratio</t>
+          <t>bottom_left_mean_std</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>bottom_left_mean_std</t>
+          <t>bottom_left_var</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>bottom_left_var</t>
+          <t>bottom_left_entropy</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>bottom_left_entropy</t>
+          <t>bottom_right_means_R</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>bottom_right_means_R</t>
+          <t>bottom_right_means_G</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>bottom_right_means_G</t>
+          <t>bottom_right_means_B</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>bottom_right_means_B</t>
+          <t>bottom_right_stds_R</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>bottom_right_stds_R</t>
+          <t>bottom_right_stds_G</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>bottom_right_stds_G</t>
+          <t>bottom_right_stds_B</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>bottom_right_stds_B</t>
+          <t>bottom_right_dominant</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>bottom_right_dominant</t>
+          <t>bottom_right_imbalance</t>
         </is>
       </c>
       <c r="BA1" s="1" t="inlineStr">
         <is>
-          <t>bottom_right_imbalance</t>
+          <t>bottom_right_green_ratio</t>
         </is>
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
-          <t>bottom_right_green_ratio</t>
+          <t>bottom_right_red_ratio</t>
         </is>
       </c>
       <c r="BC1" s="1" t="inlineStr">
         <is>
-          <t>bottom_right_red_ratio</t>
+          <t>bottom_right_blue_ratio</t>
         </is>
       </c>
       <c r="BD1" s="1" t="inlineStr">
         <is>
-          <t>bottom_right_blue_ratio</t>
+          <t>bottom_right_mean_std</t>
         </is>
       </c>
       <c r="BE1" s="1" t="inlineStr">
         <is>
-          <t>bottom_right_mean_std</t>
+          <t>bottom_right_var</t>
         </is>
       </c>
       <c r="BF1" s="1" t="inlineStr">
         <is>
-          <t>bottom_right_var</t>
+          <t>bottom_right_entropy</t>
         </is>
       </c>
       <c r="BG1" s="1" t="inlineStr">
         <is>
-          <t>bottom_right_entropy</t>
+          <t>overall_means_R</t>
         </is>
       </c>
       <c r="BH1" s="1" t="inlineStr">
         <is>
-          <t>overall_means_R</t>
+          <t>overall_means_G</t>
         </is>
       </c>
       <c r="BI1" s="1" t="inlineStr">
         <is>
-          <t>overall_means_G</t>
+          <t>overall_means_B</t>
         </is>
       </c>
       <c r="BJ1" s="1" t="inlineStr">
         <is>
-          <t>overall_means_B</t>
+          <t>overall_stds_R</t>
         </is>
       </c>
       <c r="BK1" s="1" t="inlineStr">
         <is>
-          <t>overall_stds_R</t>
+          <t>overall_stds_G</t>
         </is>
       </c>
       <c r="BL1" s="1" t="inlineStr">
         <is>
-          <t>overall_stds_G</t>
+          <t>overall_stds_B</t>
         </is>
       </c>
       <c r="BM1" s="1" t="inlineStr">
         <is>
-          <t>overall_stds_B</t>
+          <t>overall_dominant</t>
         </is>
       </c>
       <c r="BN1" s="1" t="inlineStr">
         <is>
-          <t>overall_dominant</t>
+          <t>overall_imbalance</t>
         </is>
       </c>
       <c r="BO1" s="1" t="inlineStr">
         <is>
-          <t>overall_imbalance</t>
+          <t>overall_green_ratio</t>
         </is>
       </c>
       <c r="BP1" s="1" t="inlineStr">
         <is>
-          <t>overall_green_ratio</t>
+          <t>overall_red_ratio</t>
         </is>
       </c>
       <c r="BQ1" s="1" t="inlineStr">
         <is>
-          <t>overall_red_ratio</t>
+          <t>overall_blue_ratio</t>
         </is>
       </c>
       <c r="BR1" s="1" t="inlineStr">
         <is>
-          <t>overall_blue_ratio</t>
+          <t>overall_mean_std</t>
         </is>
       </c>
       <c r="BS1" s="1" t="inlineStr">
         <is>
-          <t>overall_mean_std</t>
+          <t>overall_var</t>
         </is>
       </c>
       <c r="BT1" s="1" t="inlineStr">
-        <is>
-          <t>overall_var</t>
-        </is>
-      </c>
-      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>overall_entropy</t>
         </is>
@@ -804,229 +799,224 @@
       <c r="B2" t="b">
         <v>0</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>5280x3956</t>
-        </is>
+      <c r="C2" t="n">
+        <v>116.081</v>
       </c>
       <c r="D2" t="n">
-        <v>116.081</v>
+        <v>115.653</v>
       </c>
       <c r="E2" t="n">
-        <v>115.653</v>
+        <v>94.907</v>
       </c>
       <c r="F2" t="n">
-        <v>94.907</v>
+        <v>31.025</v>
       </c>
       <c r="G2" t="n">
-        <v>31.025</v>
+        <v>23.649</v>
       </c>
       <c r="H2" t="n">
-        <v>23.649</v>
-      </c>
-      <c r="I2" t="n">
         <v>32.778</v>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
+      <c r="J2" t="n">
+        <v>0.551</v>
+      </c>
       <c r="K2" t="n">
+        <v>1.096</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.103</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="N2" t="n">
+        <v>29.151</v>
+      </c>
+      <c r="O2" t="n">
+        <v>171.667</v>
+      </c>
+      <c r="P2" t="n">
+        <v>6.773</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>123.551</v>
+      </c>
+      <c r="R2" t="n">
+        <v>117.81</v>
+      </c>
+      <c r="S2" t="n">
+        <v>106.542</v>
+      </c>
+      <c r="T2" t="n">
+        <v>19.088</v>
+      </c>
+      <c r="U2" t="n">
+        <v>17.346</v>
+      </c>
+      <c r="V2" t="n">
+        <v>19.534</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
         <v>0.551</v>
       </c>
-      <c r="L2" t="n">
-        <v>1.096</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.103</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.819</v>
-      </c>
-      <c r="O2" t="n">
-        <v>29.151</v>
-      </c>
-      <c r="P2" t="n">
-        <v>171.667</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>6.773</v>
-      </c>
-      <c r="R2" t="n">
-        <v>123.551</v>
-      </c>
-      <c r="S2" t="n">
-        <v>117.81</v>
-      </c>
-      <c r="T2" t="n">
-        <v>106.542</v>
-      </c>
-      <c r="U2" t="n">
-        <v>19.088</v>
-      </c>
-      <c r="V2" t="n">
-        <v>17.346</v>
-      </c>
-      <c r="W2" t="n">
-        <v>19.534</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="n">
+        <v>1.024</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1.101</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.883</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>18.656</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>137.538</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>6.236</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>106.728</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>113.287</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>78.212</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>34.42</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>28.161</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>35.879</v>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.613</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1.225</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1.115</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0.711</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>32.82</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>355.8</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>7.025</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>126.599</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>124.712</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>105.024</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>32.512</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>26.247</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>33.565</v>
+      </c>
+      <c r="AY2" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="AZ2" t="n">
         <v>0.551</v>
       </c>
-      <c r="Z2" t="n">
-        <v>1.024</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.101</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0.883</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>18.656</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>137.538</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>6.236</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>106.728</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>113.287</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>78.212</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>34.42</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>28.161</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>35.879</v>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="AM2" t="n">
-        <v>0.613</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1.225</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1.115</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>0.711</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>32.82</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>355.8</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>7.025</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>126.599</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>124.712</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>105.024</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>32.512</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>26.247</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>33.565</v>
-      </c>
-      <c r="AZ2" t="inlineStr">
+      <c r="BA2" t="n">
+        <v>1.077</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>1.102</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>0.836</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>30.775</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>136.589</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>6.898</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>118.239</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>117.866</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>96.17100000000001</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>30.838</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>24.571</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>33.091</v>
+      </c>
+      <c r="BM2" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="BA2" t="n">
-        <v>0.551</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>1.077</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>1.102</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>0.836</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>30.775</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>136.589</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>6.898</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>118.239</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>117.866</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>96.17100000000001</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>30.838</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>24.571</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>33.091</v>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
+      <c r="BN2" t="n">
+        <v>0.552</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.552</v>
+        <v>1.099</v>
       </c>
       <c r="BP2" t="n">
-        <v>1.099</v>
+        <v>1.105</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.105</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.8149999999999999</v>
+        <v>29.5</v>
       </c>
       <c r="BS2" t="n">
-        <v>29.5</v>
+        <v>200.203</v>
       </c>
       <c r="BT2" t="n">
-        <v>200.203</v>
-      </c>
-      <c r="BU2" t="n">
         <v>6.859</v>
       </c>
     </row>
@@ -1039,98 +1029,96 @@
       <c r="B3" t="b">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>5280x3956</t>
-        </is>
+      <c r="C3" t="n">
+        <v>126.126</v>
       </c>
       <c r="D3" t="n">
-        <v>126.126</v>
+        <v>126.519</v>
       </c>
       <c r="E3" t="n">
-        <v>126.519</v>
+        <v>125.265</v>
       </c>
       <c r="F3" t="n">
-        <v>125.265</v>
+        <v>11.29</v>
       </c>
       <c r="G3" t="n">
-        <v>11.29</v>
+        <v>9.606</v>
       </c>
       <c r="H3" t="n">
-        <v>9.606</v>
-      </c>
-      <c r="I3" t="n">
         <v>14.542</v>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
+      <c r="J3" t="n">
+        <v>0.503</v>
+      </c>
       <c r="K3" t="n">
-        <v>0.503</v>
+        <v>1.007</v>
       </c>
       <c r="L3" t="n">
-        <v>1.007</v>
+        <v>1.002</v>
       </c>
       <c r="M3" t="n">
-        <v>1.002</v>
+        <v>0.992</v>
       </c>
       <c r="N3" t="n">
-        <v>0.992</v>
+        <v>11.813</v>
       </c>
       <c r="O3" t="n">
-        <v>11.813</v>
+        <v>24.012</v>
       </c>
       <c r="P3" t="n">
-        <v>24.012</v>
+        <v>0.602</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.602</v>
+        <v>127.477</v>
       </c>
       <c r="R3" t="n">
-        <v>127.477</v>
+        <v>127.264</v>
       </c>
       <c r="S3" t="n">
-        <v>127.264</v>
+        <v>126.85</v>
       </c>
       <c r="T3" t="n">
-        <v>126.85</v>
+        <v>3.626</v>
       </c>
       <c r="U3" t="n">
-        <v>3.626</v>
+        <v>4.197</v>
       </c>
       <c r="V3" t="n">
-        <v>4.197</v>
-      </c>
-      <c r="W3" t="n">
         <v>6.215</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
+      <c r="X3" t="n">
+        <v>0.502</v>
+      </c>
       <c r="Y3" t="n">
-        <v>0.502</v>
+        <v>1.001</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.001</v>
+        <v>1.003</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.003</v>
+        <v>0.996</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.996</v>
+        <v>4.679</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.679</v>
+        <v>3.011</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.011</v>
+        <v>0.473</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.473</v>
+        <v>128</v>
       </c>
       <c r="AF3" t="n">
         <v>128</v>
@@ -1139,42 +1127,42 @@
         <v>128</v>
       </c>
       <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS3" t="n">
         <v>128</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="AM3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>-0</v>
       </c>
       <c r="AT3" t="n">
         <v>128</v>
@@ -1183,7 +1171,7 @@
         <v>128</v>
       </c>
       <c r="AV3" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="AW3" t="n">
         <v>0</v>
@@ -1191,16 +1179,16 @@
       <c r="AX3" t="n">
         <v>0</v>
       </c>
-      <c r="AY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ3" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
+      <c r="AZ3" t="n">
+        <v>0.5</v>
+      </c>
       <c r="BA3" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="BB3" t="n">
         <v>1</v>
@@ -1209,59 +1197,56 @@
         <v>1</v>
       </c>
       <c r="BD3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE3" t="n">
         <v>0</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0</v>
+        <v>127.401</v>
       </c>
       <c r="BH3" t="n">
-        <v>127.401</v>
+        <v>127.446</v>
       </c>
       <c r="BI3" t="n">
-        <v>127.446</v>
+        <v>127.029</v>
       </c>
       <c r="BJ3" t="n">
-        <v>127.029</v>
+        <v>5.979</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.979</v>
+        <v>5.277</v>
       </c>
       <c r="BL3" t="n">
-        <v>5.277</v>
-      </c>
-      <c r="BM3" t="n">
         <v>7.986</v>
       </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BM3" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
+      <c r="BN3" t="n">
+        <v>0.501</v>
+      </c>
       <c r="BO3" t="n">
-        <v>0.501</v>
+        <v>1.002</v>
       </c>
       <c r="BP3" t="n">
-        <v>1.002</v>
+        <v>1.001</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.001</v>
+        <v>0.997</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.997</v>
+        <v>6.414</v>
       </c>
       <c r="BS3" t="n">
-        <v>6.414</v>
+        <v>6.755</v>
       </c>
       <c r="BT3" t="n">
-        <v>6.755</v>
-      </c>
-      <c r="BU3" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -1274,98 +1259,96 @@
       <c r="B4" t="b">
         <v>1</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>5280x3956</t>
-        </is>
+      <c r="C4" t="n">
+        <v>122.398</v>
       </c>
       <c r="D4" t="n">
-        <v>122.398</v>
+        <v>123.434</v>
       </c>
       <c r="E4" t="n">
-        <v>123.434</v>
+        <v>121.243</v>
       </c>
       <c r="F4" t="n">
-        <v>121.243</v>
+        <v>18.239</v>
       </c>
       <c r="G4" t="n">
-        <v>18.239</v>
+        <v>15.265</v>
       </c>
       <c r="H4" t="n">
-        <v>15.265</v>
-      </c>
-      <c r="I4" t="n">
         <v>21.395</v>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
+      <c r="J4" t="n">
+        <v>0.507</v>
+      </c>
       <c r="K4" t="n">
-        <v>0.507</v>
+        <v>1.013</v>
       </c>
       <c r="L4" t="n">
-        <v>1.013</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>0.986</v>
       </c>
       <c r="N4" t="n">
-        <v>0.986</v>
+        <v>18.3</v>
       </c>
       <c r="O4" t="n">
-        <v>18.3</v>
+        <v>20.117</v>
       </c>
       <c r="P4" t="n">
-        <v>20.117</v>
+        <v>1.076</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.076</v>
+        <v>126.441</v>
       </c>
       <c r="R4" t="n">
-        <v>126.441</v>
+        <v>126.006</v>
       </c>
       <c r="S4" t="n">
-        <v>126.006</v>
+        <v>124.863</v>
       </c>
       <c r="T4" t="n">
-        <v>124.863</v>
+        <v>9.403</v>
       </c>
       <c r="U4" t="n">
-        <v>9.403</v>
+        <v>9.148</v>
       </c>
       <c r="V4" t="n">
-        <v>9.148</v>
-      </c>
-      <c r="W4" t="n">
         <v>12.617</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
+      <c r="X4" t="n">
+        <v>0.504</v>
+      </c>
       <c r="Y4" t="n">
-        <v>0.504</v>
+        <v>1.003</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.003</v>
+        <v>1.008</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.008</v>
+        <v>0.989</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.989</v>
+        <v>10.389</v>
       </c>
       <c r="AC4" t="n">
-        <v>10.389</v>
+        <v>11.787</v>
       </c>
       <c r="AD4" t="n">
-        <v>11.787</v>
+        <v>1.006</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.006</v>
+        <v>128</v>
       </c>
       <c r="AF4" t="n">
         <v>128</v>
@@ -1374,42 +1357,42 @@
         <v>128</v>
       </c>
       <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS4" t="n">
         <v>128</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="AM4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>-0</v>
       </c>
       <c r="AT4" t="n">
         <v>128</v>
@@ -1418,7 +1401,7 @@
         <v>128</v>
       </c>
       <c r="AV4" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="AW4" t="n">
         <v>0</v>
@@ -1426,16 +1409,16 @@
       <c r="AX4" t="n">
         <v>0</v>
       </c>
-      <c r="AY4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ4" t="inlineStr">
+      <c r="AY4" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
+      <c r="AZ4" t="n">
+        <v>0.5</v>
+      </c>
       <c r="BA4" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="BB4" t="n">
         <v>1</v>
@@ -1444,59 +1427,56 @@
         <v>1</v>
       </c>
       <c r="BD4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE4" t="n">
         <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG4" t="n">
-        <v>-0</v>
+        <v>126.21</v>
       </c>
       <c r="BH4" t="n">
-        <v>126.21</v>
+        <v>126.36</v>
       </c>
       <c r="BI4" t="n">
-        <v>126.36</v>
+        <v>125.527</v>
       </c>
       <c r="BJ4" t="n">
-        <v>125.527</v>
+        <v>10.513</v>
       </c>
       <c r="BK4" t="n">
-        <v>10.513</v>
+        <v>9.093</v>
       </c>
       <c r="BL4" t="n">
-        <v>9.093</v>
-      </c>
-      <c r="BM4" t="n">
         <v>12.727</v>
       </c>
-      <c r="BN4" t="inlineStr">
+      <c r="BM4" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
+      <c r="BN4" t="n">
+        <v>0.502</v>
+      </c>
       <c r="BO4" t="n">
-        <v>0.502</v>
+        <v>1.004</v>
       </c>
       <c r="BP4" t="n">
-        <v>1.004</v>
+        <v>1.002</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.002</v>
+        <v>0.994</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.994</v>
+        <v>10.778</v>
       </c>
       <c r="BS4" t="n">
-        <v>10.778</v>
+        <v>7.974</v>
       </c>
       <c r="BT4" t="n">
-        <v>7.974</v>
-      </c>
-      <c r="BU4" t="n">
         <v>0.589</v>
       </c>
     </row>
@@ -1509,98 +1489,96 @@
       <c r="B5" t="b">
         <v>1</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>5280x3956</t>
-        </is>
+      <c r="C5" t="n">
+        <v>119.572</v>
       </c>
       <c r="D5" t="n">
-        <v>119.572</v>
+        <v>122.236</v>
       </c>
       <c r="E5" t="n">
-        <v>122.236</v>
+        <v>116.218</v>
       </c>
       <c r="F5" t="n">
-        <v>116.218</v>
+        <v>20.464</v>
       </c>
       <c r="G5" t="n">
-        <v>20.464</v>
+        <v>15.947</v>
       </c>
       <c r="H5" t="n">
-        <v>15.947</v>
-      </c>
-      <c r="I5" t="n">
         <v>26.197</v>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
+      <c r="J5" t="n">
+        <v>0.518</v>
+      </c>
       <c r="K5" t="n">
-        <v>0.518</v>
+        <v>1.037</v>
       </c>
       <c r="L5" t="n">
-        <v>1.037</v>
+        <v>1.003</v>
       </c>
       <c r="M5" t="n">
-        <v>1.003</v>
+        <v>0.961</v>
       </c>
       <c r="N5" t="n">
-        <v>0.961</v>
+        <v>20.869</v>
       </c>
       <c r="O5" t="n">
-        <v>20.869</v>
+        <v>55.915</v>
       </c>
       <c r="P5" t="n">
-        <v>55.915</v>
+        <v>1.914</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.914</v>
+        <v>124.055</v>
       </c>
       <c r="R5" t="n">
-        <v>124.055</v>
+        <v>123.95</v>
       </c>
       <c r="S5" t="n">
-        <v>123.95</v>
+        <v>120.61</v>
       </c>
       <c r="T5" t="n">
-        <v>120.61</v>
+        <v>18.994</v>
       </c>
       <c r="U5" t="n">
-        <v>18.994</v>
+        <v>15.141</v>
       </c>
       <c r="V5" t="n">
-        <v>15.141</v>
-      </c>
-      <c r="W5" t="n">
         <v>21.429</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
+      <c r="X5" t="n">
+        <v>0.507</v>
+      </c>
       <c r="Y5" t="n">
-        <v>0.507</v>
+        <v>1.013</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.013</v>
+        <v>1.015</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.015</v>
+        <v>0.973</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.973</v>
+        <v>18.522</v>
       </c>
       <c r="AC5" t="n">
-        <v>18.522</v>
+        <v>29.586</v>
       </c>
       <c r="AD5" t="n">
-        <v>29.586</v>
+        <v>1.939</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.939</v>
+        <v>128</v>
       </c>
       <c r="AF5" t="n">
         <v>128</v>
@@ -1609,42 +1587,42 @@
         <v>128</v>
       </c>
       <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS5" t="n">
         <v>128</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="AM5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>-0</v>
       </c>
       <c r="AT5" t="n">
         <v>128</v>
@@ -1653,7 +1631,7 @@
         <v>128</v>
       </c>
       <c r="AV5" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="AW5" t="n">
         <v>0</v>
@@ -1661,16 +1639,16 @@
       <c r="AX5" t="n">
         <v>0</v>
       </c>
-      <c r="AY5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ5" t="inlineStr">
+      <c r="AY5" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
+      <c r="AZ5" t="n">
+        <v>0.5</v>
+      </c>
       <c r="BA5" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="BB5" t="n">
         <v>1</v>
@@ -1679,59 +1657,56 @@
         <v>1</v>
       </c>
       <c r="BD5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0</v>
+        <v>124.907</v>
       </c>
       <c r="BH5" t="n">
-        <v>124.907</v>
+        <v>125.546</v>
       </c>
       <c r="BI5" t="n">
-        <v>125.546</v>
+        <v>123.207</v>
       </c>
       <c r="BJ5" t="n">
-        <v>123.207</v>
+        <v>14.386</v>
       </c>
       <c r="BK5" t="n">
-        <v>14.386</v>
+        <v>11.282</v>
       </c>
       <c r="BL5" t="n">
-        <v>11.282</v>
-      </c>
-      <c r="BM5" t="n">
         <v>17.657</v>
       </c>
-      <c r="BN5" t="inlineStr">
+      <c r="BM5" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
+      <c r="BN5" t="n">
+        <v>0.506</v>
+      </c>
       <c r="BO5" t="n">
-        <v>0.506</v>
+        <v>1.012</v>
       </c>
       <c r="BP5" t="n">
-        <v>1.012</v>
+        <v>1.004</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.004</v>
+        <v>0.984</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.984</v>
+        <v>14.442</v>
       </c>
       <c r="BS5" t="n">
-        <v>14.442</v>
+        <v>21.358</v>
       </c>
       <c r="BT5" t="n">
-        <v>21.358</v>
-      </c>
-      <c r="BU5" t="n">
         <v>1.082</v>
       </c>
     </row>
@@ -1744,98 +1719,96 @@
       <c r="B6" t="b">
         <v>1</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>5280x3956</t>
-        </is>
+      <c r="C6" t="n">
+        <v>121.91</v>
       </c>
       <c r="D6" t="n">
-        <v>121.91</v>
+        <v>124.442</v>
       </c>
       <c r="E6" t="n">
-        <v>124.442</v>
+        <v>119.413</v>
       </c>
       <c r="F6" t="n">
-        <v>119.413</v>
+        <v>20.885</v>
       </c>
       <c r="G6" t="n">
-        <v>20.885</v>
+        <v>13.97</v>
       </c>
       <c r="H6" t="n">
-        <v>13.97</v>
-      </c>
-      <c r="I6" t="n">
         <v>24.579</v>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
+      <c r="J6" t="n">
+        <v>0.516</v>
+      </c>
       <c r="K6" t="n">
-        <v>0.516</v>
+        <v>1.031</v>
       </c>
       <c r="L6" t="n">
-        <v>1.031</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>0.969</v>
       </c>
       <c r="N6" t="n">
-        <v>0.969</v>
+        <v>19.812</v>
       </c>
       <c r="O6" t="n">
-        <v>19.812</v>
+        <v>50.078</v>
       </c>
       <c r="P6" t="n">
-        <v>50.078</v>
+        <v>1.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.5</v>
+        <v>122.776</v>
       </c>
       <c r="R6" t="n">
-        <v>122.776</v>
+        <v>124.386</v>
       </c>
       <c r="S6" t="n">
-        <v>124.386</v>
+        <v>120.623</v>
       </c>
       <c r="T6" t="n">
-        <v>120.623</v>
+        <v>21.599</v>
       </c>
       <c r="U6" t="n">
-        <v>21.599</v>
+        <v>15.081</v>
       </c>
       <c r="V6" t="n">
-        <v>15.081</v>
-      </c>
-      <c r="W6" t="n">
         <v>23.799</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
+      <c r="X6" t="n">
+        <v>0.511</v>
+      </c>
       <c r="Y6" t="n">
-        <v>0.511</v>
+        <v>1.022</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.022</v>
+        <v>1.002</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.002</v>
+        <v>0.976</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.976</v>
+        <v>20.159</v>
       </c>
       <c r="AC6" t="n">
-        <v>20.159</v>
+        <v>36.239</v>
       </c>
       <c r="AD6" t="n">
-        <v>36.239</v>
+        <v>1.475</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.475</v>
+        <v>128</v>
       </c>
       <c r="AF6" t="n">
         <v>128</v>
@@ -1844,42 +1817,42 @@
         <v>128</v>
       </c>
       <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS6" t="n">
         <v>128</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="AM6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>-0</v>
       </c>
       <c r="AT6" t="n">
         <v>128</v>
@@ -1888,7 +1861,7 @@
         <v>128</v>
       </c>
       <c r="AV6" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="AW6" t="n">
         <v>0</v>
@@ -1896,16 +1869,16 @@
       <c r="AX6" t="n">
         <v>0</v>
       </c>
-      <c r="AY6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ6" t="inlineStr">
+      <c r="AY6" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
+      <c r="AZ6" t="n">
+        <v>0.5</v>
+      </c>
       <c r="BA6" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="BB6" t="n">
         <v>1</v>
@@ -1914,59 +1887,56 @@
         <v>1</v>
       </c>
       <c r="BD6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0</v>
+        <v>125.172</v>
       </c>
       <c r="BH6" t="n">
-        <v>125.172</v>
+        <v>126.207</v>
       </c>
       <c r="BI6" t="n">
-        <v>126.207</v>
+        <v>124.009</v>
       </c>
       <c r="BJ6" t="n">
-        <v>124.009</v>
+        <v>15.29</v>
       </c>
       <c r="BK6" t="n">
-        <v>15.29</v>
+        <v>10.434</v>
       </c>
       <c r="BL6" t="n">
-        <v>10.434</v>
-      </c>
-      <c r="BM6" t="n">
         <v>17.571</v>
       </c>
-      <c r="BN6" t="inlineStr">
+      <c r="BM6" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
+      <c r="BN6" t="n">
+        <v>0.506</v>
+      </c>
       <c r="BO6" t="n">
-        <v>0.506</v>
+        <v>1.013</v>
       </c>
       <c r="BP6" t="n">
-        <v>1.013</v>
+        <v>1.001</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.001</v>
+        <v>0.987</v>
       </c>
       <c r="BR6" t="n">
-        <v>0.987</v>
+        <v>14.431</v>
       </c>
       <c r="BS6" t="n">
-        <v>14.431</v>
+        <v>21.566</v>
       </c>
       <c r="BT6" t="n">
-        <v>21.566</v>
-      </c>
-      <c r="BU6" t="n">
         <v>0.819</v>
       </c>
     </row>
@@ -1979,98 +1949,96 @@
       <c r="B7" t="b">
         <v>1</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>5280x3956</t>
-        </is>
+      <c r="C7" t="n">
+        <v>113.795</v>
       </c>
       <c r="D7" t="n">
-        <v>113.795</v>
+        <v>117.904</v>
       </c>
       <c r="E7" t="n">
-        <v>117.904</v>
+        <v>110.991</v>
       </c>
       <c r="F7" t="n">
-        <v>110.991</v>
+        <v>45.006</v>
       </c>
       <c r="G7" t="n">
-        <v>45.006</v>
+        <v>33.685</v>
       </c>
       <c r="H7" t="n">
-        <v>33.685</v>
-      </c>
-      <c r="I7" t="n">
         <v>43.229</v>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
+      <c r="J7" t="n">
+        <v>0.525</v>
+      </c>
       <c r="K7" t="n">
-        <v>0.525</v>
+        <v>1.049</v>
       </c>
       <c r="L7" t="n">
-        <v>1.049</v>
+        <v>0.994</v>
       </c>
       <c r="M7" t="n">
-        <v>0.994</v>
+        <v>0.958</v>
       </c>
       <c r="N7" t="n">
-        <v>0.958</v>
+        <v>40.64</v>
       </c>
       <c r="O7" t="n">
-        <v>40.64</v>
+        <v>46.392</v>
       </c>
       <c r="P7" t="n">
-        <v>46.392</v>
+        <v>1.903</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.903</v>
+        <v>110.218</v>
       </c>
       <c r="R7" t="n">
-        <v>110.218</v>
+        <v>115.929</v>
       </c>
       <c r="S7" t="n">
-        <v>115.929</v>
+        <v>108.817</v>
       </c>
       <c r="T7" t="n">
-        <v>108.817</v>
+        <v>42.329</v>
       </c>
       <c r="U7" t="n">
-        <v>42.329</v>
+        <v>30.676</v>
       </c>
       <c r="V7" t="n">
-        <v>30.676</v>
-      </c>
-      <c r="W7" t="n">
         <v>42.976</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
+      <c r="X7" t="n">
+        <v>0.529</v>
+      </c>
       <c r="Y7" t="n">
-        <v>0.529</v>
+        <v>1.059</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.059</v>
+        <v>0.981</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.981</v>
+        <v>0.962</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.962</v>
+        <v>38.66</v>
       </c>
       <c r="AC7" t="n">
-        <v>38.66</v>
+        <v>59.734</v>
       </c>
       <c r="AD7" t="n">
-        <v>59.734</v>
+        <v>1.732</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.732</v>
+        <v>128</v>
       </c>
       <c r="AF7" t="n">
         <v>128</v>
@@ -2079,42 +2047,42 @@
         <v>128</v>
       </c>
       <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS7" t="n">
         <v>128</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="AM7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>-0</v>
       </c>
       <c r="AT7" t="n">
         <v>128</v>
@@ -2123,7 +2091,7 @@
         <v>128</v>
       </c>
       <c r="AV7" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="AW7" t="n">
         <v>0</v>
@@ -2131,16 +2099,16 @@
       <c r="AX7" t="n">
         <v>0</v>
       </c>
-      <c r="AY7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ7" t="inlineStr">
+      <c r="AY7" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
+      <c r="AZ7" t="n">
+        <v>0.5</v>
+      </c>
       <c r="BA7" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="BB7" t="n">
         <v>1</v>
@@ -2149,59 +2117,56 @@
         <v>1</v>
       </c>
       <c r="BD7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0</v>
+        <v>120.003</v>
       </c>
       <c r="BH7" t="n">
-        <v>120.003</v>
+        <v>122.458</v>
       </c>
       <c r="BI7" t="n">
-        <v>122.458</v>
+        <v>118.952</v>
       </c>
       <c r="BJ7" t="n">
-        <v>118.952</v>
+        <v>31.935</v>
       </c>
       <c r="BK7" t="n">
-        <v>31.935</v>
+        <v>23.455</v>
       </c>
       <c r="BL7" t="n">
-        <v>23.455</v>
-      </c>
-      <c r="BM7" t="n">
         <v>31.802</v>
       </c>
-      <c r="BN7" t="inlineStr">
+      <c r="BM7" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
+      <c r="BN7" t="n">
+        <v>0.512</v>
+      </c>
       <c r="BO7" t="n">
-        <v>0.512</v>
+        <v>1.025</v>
       </c>
       <c r="BP7" t="n">
-        <v>1.025</v>
+        <v>0.994</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.994</v>
+        <v>0.981</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.981</v>
+        <v>29.064</v>
       </c>
       <c r="BS7" t="n">
-        <v>29.064</v>
+        <v>26.518</v>
       </c>
       <c r="BT7" t="n">
-        <v>26.518</v>
-      </c>
-      <c r="BU7" t="n">
         <v>1.029</v>
       </c>
     </row>
@@ -2214,98 +2179,96 @@
       <c r="B8" t="b">
         <v>1</v>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>5280x3956</t>
-        </is>
+      <c r="C8" t="n">
+        <v>126.369</v>
       </c>
       <c r="D8" t="n">
-        <v>126.369</v>
+        <v>127.251</v>
       </c>
       <c r="E8" t="n">
-        <v>127.251</v>
+        <v>124.511</v>
       </c>
       <c r="F8" t="n">
-        <v>124.511</v>
+        <v>15.2</v>
       </c>
       <c r="G8" t="n">
-        <v>15.2</v>
+        <v>11.429</v>
       </c>
       <c r="H8" t="n">
-        <v>11.429</v>
-      </c>
-      <c r="I8" t="n">
         <v>15.984</v>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
+      <c r="J8" t="n">
+        <v>0.507</v>
+      </c>
       <c r="K8" t="n">
-        <v>0.507</v>
+        <v>1.014</v>
       </c>
       <c r="L8" t="n">
-        <v>1.014</v>
+        <v>1.004</v>
       </c>
       <c r="M8" t="n">
+        <v>0.982</v>
+      </c>
+      <c r="N8" t="n">
+        <v>14.204</v>
+      </c>
+      <c r="O8" t="n">
+        <v>27.89</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.991</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>127.569</v>
+      </c>
+      <c r="R8" t="n">
+        <v>127.886</v>
+      </c>
+      <c r="S8" t="n">
+        <v>126.124</v>
+      </c>
+      <c r="T8" t="n">
+        <v>13.632</v>
+      </c>
+      <c r="U8" t="n">
+        <v>10.086</v>
+      </c>
+      <c r="V8" t="n">
+        <v>13.63</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>0.504</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.008</v>
+      </c>
+      <c r="Z8" t="n">
         <v>1.004</v>
       </c>
-      <c r="N8" t="n">
-        <v>0.982</v>
-      </c>
-      <c r="O8" t="n">
-        <v>14.204</v>
-      </c>
-      <c r="P8" t="n">
-        <v>27.89</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0.991</v>
-      </c>
-      <c r="R8" t="n">
-        <v>127.569</v>
-      </c>
-      <c r="S8" t="n">
-        <v>127.886</v>
-      </c>
-      <c r="T8" t="n">
-        <v>126.124</v>
-      </c>
-      <c r="U8" t="n">
-        <v>13.632</v>
-      </c>
-      <c r="V8" t="n">
-        <v>10.086</v>
-      </c>
-      <c r="W8" t="n">
-        <v>13.63</v>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="Y8" t="n">
-        <v>0.504</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.008</v>
-      </c>
       <c r="AA8" t="n">
-        <v>1.004</v>
+        <v>0.987</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.987</v>
+        <v>12.45</v>
       </c>
       <c r="AC8" t="n">
-        <v>12.45</v>
+        <v>17.574</v>
       </c>
       <c r="AD8" t="n">
-        <v>17.574</v>
+        <v>0.9</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.9</v>
+        <v>128</v>
       </c>
       <c r="AF8" t="n">
         <v>128</v>
@@ -2314,42 +2277,42 @@
         <v>128</v>
       </c>
       <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS8" t="n">
         <v>128</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="AM8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>-0</v>
       </c>
       <c r="AT8" t="n">
         <v>128</v>
@@ -2358,7 +2321,7 @@
         <v>128</v>
       </c>
       <c r="AV8" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="AW8" t="n">
         <v>0</v>
@@ -2366,16 +2329,16 @@
       <c r="AX8" t="n">
         <v>0</v>
       </c>
-      <c r="AY8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ8" t="inlineStr">
+      <c r="AY8" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
+      <c r="AZ8" t="n">
+        <v>0.5</v>
+      </c>
       <c r="BA8" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="BB8" t="n">
         <v>1</v>
@@ -2384,59 +2347,56 @@
         <v>1</v>
       </c>
       <c r="BD8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE8" t="n">
         <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG8" t="n">
-        <v>-0</v>
+        <v>127.484</v>
       </c>
       <c r="BH8" t="n">
-        <v>127.484</v>
+        <v>127.784</v>
       </c>
       <c r="BI8" t="n">
-        <v>127.784</v>
+        <v>126.659</v>
       </c>
       <c r="BJ8" t="n">
-        <v>126.659</v>
+        <v>10.23</v>
       </c>
       <c r="BK8" t="n">
-        <v>10.23</v>
+        <v>7.628</v>
       </c>
       <c r="BL8" t="n">
-        <v>7.628</v>
-      </c>
-      <c r="BM8" t="n">
         <v>10.604</v>
       </c>
-      <c r="BN8" t="inlineStr">
+      <c r="BM8" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
+      <c r="BN8" t="n">
+        <v>0.503</v>
+      </c>
       <c r="BO8" t="n">
-        <v>0.503</v>
+        <v>1.006</v>
       </c>
       <c r="BP8" t="n">
-        <v>1.006</v>
+        <v>1.002</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.002</v>
+        <v>0.992</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.992</v>
+        <v>9.487</v>
       </c>
       <c r="BS8" t="n">
-        <v>9.487</v>
+        <v>11.355</v>
       </c>
       <c r="BT8" t="n">
-        <v>11.355</v>
-      </c>
-      <c r="BU8" t="n">
         <v>0.519</v>
       </c>
     </row>
@@ -2449,229 +2409,224 @@
       <c r="B9" t="b">
         <v>0</v>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>5280x3956</t>
-        </is>
+      <c r="C9" t="n">
+        <v>109.017</v>
       </c>
       <c r="D9" t="n">
-        <v>109.017</v>
+        <v>121.814</v>
       </c>
       <c r="E9" t="n">
-        <v>121.814</v>
+        <v>83.931</v>
       </c>
       <c r="F9" t="n">
-        <v>83.931</v>
+        <v>48.555</v>
       </c>
       <c r="G9" t="n">
-        <v>48.555</v>
+        <v>40.157</v>
       </c>
       <c r="H9" t="n">
-        <v>40.157</v>
-      </c>
-      <c r="I9" t="n">
         <v>39.052</v>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
+      <c r="J9" t="n">
+        <v>0.631</v>
+      </c>
       <c r="K9" t="n">
-        <v>0.631</v>
+        <v>1.263</v>
       </c>
       <c r="L9" t="n">
-        <v>1.263</v>
+        <v>1.06</v>
       </c>
       <c r="M9" t="n">
-        <v>1.06</v>
+        <v>0.727</v>
       </c>
       <c r="N9" t="n">
-        <v>0.727</v>
+        <v>42.588</v>
       </c>
       <c r="O9" t="n">
-        <v>42.588</v>
+        <v>620.151</v>
       </c>
       <c r="P9" t="n">
-        <v>620.151</v>
+        <v>7.315</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.315</v>
+        <v>132.633</v>
       </c>
       <c r="R9" t="n">
-        <v>132.633</v>
+        <v>136.04</v>
       </c>
       <c r="S9" t="n">
-        <v>136.04</v>
+        <v>107.792</v>
       </c>
       <c r="T9" t="n">
-        <v>107.792</v>
+        <v>51.106</v>
       </c>
       <c r="U9" t="n">
-        <v>51.106</v>
+        <v>38.355</v>
       </c>
       <c r="V9" t="n">
-        <v>38.355</v>
-      </c>
-      <c r="W9" t="n">
         <v>47.487</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
+      <c r="X9" t="n">
+        <v>0.5659999999999999</v>
+      </c>
       <c r="Y9" t="n">
-        <v>0.5659999999999999</v>
+        <v>1.132</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.132</v>
+        <v>1.088</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.088</v>
+        <v>0.802</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.802</v>
+        <v>45.649</v>
       </c>
       <c r="AC9" t="n">
-        <v>45.649</v>
+        <v>413.589</v>
       </c>
       <c r="AD9" t="n">
-        <v>413.589</v>
+        <v>7.346</v>
       </c>
       <c r="AE9" t="n">
-        <v>7.346</v>
+        <v>109.962</v>
       </c>
       <c r="AF9" t="n">
-        <v>109.962</v>
+        <v>125.55</v>
       </c>
       <c r="AG9" t="n">
-        <v>125.55</v>
+        <v>80.771</v>
       </c>
       <c r="AH9" t="n">
-        <v>80.771</v>
+        <v>50.019</v>
       </c>
       <c r="AI9" t="n">
-        <v>50.019</v>
+        <v>41.6</v>
       </c>
       <c r="AJ9" t="n">
-        <v>41.6</v>
-      </c>
-      <c r="AK9" t="n">
         <v>40.593</v>
       </c>
-      <c r="AL9" t="inlineStr">
+      <c r="AK9" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
+      <c r="AL9" t="n">
+        <v>0.658</v>
+      </c>
       <c r="AM9" t="n">
-        <v>0.658</v>
+        <v>1.317</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.317</v>
+        <v>1.066</v>
       </c>
       <c r="AO9" t="n">
-        <v>1.066</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.6860000000000001</v>
+        <v>44.071</v>
       </c>
       <c r="AQ9" t="n">
-        <v>44.071</v>
+        <v>754.211</v>
       </c>
       <c r="AR9" t="n">
-        <v>754.211</v>
+        <v>7.401</v>
       </c>
       <c r="AS9" t="n">
-        <v>7.401</v>
+        <v>136.668</v>
       </c>
       <c r="AT9" t="n">
-        <v>136.668</v>
+        <v>143.008</v>
       </c>
       <c r="AU9" t="n">
-        <v>143.008</v>
+        <v>109.931</v>
       </c>
       <c r="AV9" t="n">
-        <v>109.931</v>
+        <v>51.51</v>
       </c>
       <c r="AW9" t="n">
-        <v>51.51</v>
+        <v>37.857</v>
       </c>
       <c r="AX9" t="n">
-        <v>37.857</v>
-      </c>
-      <c r="AY9" t="n">
         <v>49.072</v>
       </c>
-      <c r="AZ9" t="inlineStr">
+      <c r="AY9" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
+      <c r="AZ9" t="n">
+        <v>0.58</v>
+      </c>
       <c r="BA9" t="n">
-        <v>0.58</v>
+        <v>1.16</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.16</v>
+        <v>1.081</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.081</v>
+        <v>0.786</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.786</v>
+        <v>46.147</v>
       </c>
       <c r="BE9" t="n">
-        <v>46.147</v>
+        <v>317.733</v>
       </c>
       <c r="BF9" t="n">
-        <v>317.733</v>
+        <v>7.26</v>
       </c>
       <c r="BG9" t="n">
-        <v>7.26</v>
+        <v>122.07</v>
       </c>
       <c r="BH9" t="n">
-        <v>122.07</v>
+        <v>131.603</v>
       </c>
       <c r="BI9" t="n">
-        <v>131.603</v>
+        <v>95.60599999999999</v>
       </c>
       <c r="BJ9" t="n">
-        <v>95.60599999999999</v>
+        <v>51.88</v>
       </c>
       <c r="BK9" t="n">
-        <v>51.88</v>
+        <v>40.403</v>
       </c>
       <c r="BL9" t="n">
-        <v>40.403</v>
-      </c>
-      <c r="BM9" t="n">
         <v>46.222</v>
       </c>
-      <c r="BN9" t="inlineStr">
+      <c r="BM9" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
+      <c r="BN9" t="n">
+        <v>0.605</v>
+      </c>
       <c r="BO9" t="n">
-        <v>0.605</v>
+        <v>1.209</v>
       </c>
       <c r="BP9" t="n">
-        <v>1.209</v>
+        <v>1.075</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.075</v>
+        <v>0.754</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.754</v>
+        <v>46.169</v>
       </c>
       <c r="BS9" t="n">
-        <v>46.169</v>
+        <v>525.857</v>
       </c>
       <c r="BT9" t="n">
-        <v>525.857</v>
-      </c>
-      <c r="BU9" t="n">
         <v>7.487</v>
       </c>
     </row>
@@ -2684,229 +2639,224 @@
       <c r="B10" t="b">
         <v>1</v>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>5280x3956</t>
-        </is>
+      <c r="C10" t="n">
+        <v>31.213</v>
       </c>
       <c r="D10" t="n">
-        <v>31.213</v>
+        <v>53.255</v>
       </c>
       <c r="E10" t="n">
-        <v>53.255</v>
+        <v>22.408</v>
       </c>
       <c r="F10" t="n">
-        <v>22.408</v>
+        <v>58.037</v>
       </c>
       <c r="G10" t="n">
-        <v>58.037</v>
+        <v>37.763</v>
       </c>
       <c r="H10" t="n">
-        <v>37.763</v>
-      </c>
-      <c r="I10" t="n">
         <v>41.378</v>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
+      <c r="J10" t="n">
+        <v>0.993</v>
+      </c>
       <c r="K10" t="n">
-        <v>0.993</v>
+        <v>1.986</v>
       </c>
       <c r="L10" t="n">
-        <v>1.986</v>
+        <v>0.825</v>
       </c>
       <c r="M10" t="n">
-        <v>0.825</v>
+        <v>0.531</v>
       </c>
       <c r="N10" t="n">
-        <v>0.531</v>
+        <v>45.726</v>
       </c>
       <c r="O10" t="n">
-        <v>45.726</v>
+        <v>42.939</v>
       </c>
       <c r="P10" t="n">
-        <v>42.939</v>
+        <v>4.161</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.161</v>
+        <v>27.192</v>
       </c>
       <c r="R10" t="n">
-        <v>27.192</v>
+        <v>52.583</v>
       </c>
       <c r="S10" t="n">
-        <v>52.583</v>
+        <v>20.6</v>
       </c>
       <c r="T10" t="n">
-        <v>20.6</v>
+        <v>50.801</v>
       </c>
       <c r="U10" t="n">
-        <v>50.801</v>
+        <v>33.561</v>
       </c>
       <c r="V10" t="n">
-        <v>33.561</v>
-      </c>
-      <c r="W10" t="n">
         <v>38.577</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
+      <c r="X10" t="n">
+        <v>1.1</v>
+      </c>
       <c r="Y10" t="n">
-        <v>1.1</v>
+        <v>2.201</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.201</v>
+        <v>0.743</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.743</v>
+        <v>0.516</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.516</v>
+        <v>40.979</v>
       </c>
       <c r="AC10" t="n">
-        <v>40.979</v>
+        <v>35.757</v>
       </c>
       <c r="AD10" t="n">
-        <v>35.757</v>
+        <v>3.297</v>
       </c>
       <c r="AE10" t="n">
-        <v>3.297</v>
+        <v>0.01</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.01</v>
+        <v>32.345</v>
       </c>
       <c r="AG10" t="n">
-        <v>32.345</v>
+        <v>0.034</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.034</v>
+        <v>0.419</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.419</v>
+        <v>4.194</v>
       </c>
       <c r="AJ10" t="n">
-        <v>4.194</v>
-      </c>
-      <c r="AK10" t="n">
         <v>0.628</v>
       </c>
-      <c r="AL10" t="inlineStr">
+      <c r="AK10" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
+      <c r="AL10" t="n">
+        <v>737.229</v>
+      </c>
       <c r="AM10" t="n">
-        <v>737.229</v>
+        <v>1474.457</v>
       </c>
       <c r="AN10" t="n">
-        <v>1474.457</v>
+        <v>0.001</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.002</v>
+        <v>1.747</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.747</v>
+        <v>2.287</v>
       </c>
       <c r="AR10" t="n">
-        <v>2.287</v>
+        <v>2.218</v>
       </c>
       <c r="AS10" t="n">
-        <v>2.218</v>
+        <v>0.153</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.153</v>
+        <v>35.475</v>
       </c>
       <c r="AU10" t="n">
-        <v>35.475</v>
+        <v>0.399</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.399</v>
+        <v>1.613</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.613</v>
+        <v>7.087</v>
       </c>
       <c r="AX10" t="n">
-        <v>7.087</v>
-      </c>
-      <c r="AY10" t="n">
         <v>3.476</v>
       </c>
-      <c r="AZ10" t="inlineStr">
+      <c r="AY10" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
+      <c r="AZ10" t="n">
+        <v>64.246</v>
+      </c>
       <c r="BA10" t="n">
-        <v>64.246</v>
+        <v>128.491</v>
       </c>
       <c r="BB10" t="n">
-        <v>128.491</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.022</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.022</v>
+        <v>4.059</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.059</v>
+        <v>5.528</v>
       </c>
       <c r="BF10" t="n">
-        <v>5.528</v>
+        <v>2.473</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.473</v>
+        <v>14.642</v>
       </c>
       <c r="BH10" t="n">
-        <v>14.642</v>
+        <v>43.415</v>
       </c>
       <c r="BI10" t="n">
-        <v>43.415</v>
+        <v>10.86</v>
       </c>
       <c r="BJ10" t="n">
-        <v>10.86</v>
+        <v>41.255</v>
       </c>
       <c r="BK10" t="n">
-        <v>41.255</v>
+        <v>27.325</v>
       </c>
       <c r="BL10" t="n">
-        <v>27.325</v>
-      </c>
-      <c r="BM10" t="n">
         <v>30.281</v>
       </c>
-      <c r="BN10" t="inlineStr">
+      <c r="BM10" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
+      <c r="BN10" t="n">
+        <v>1.702</v>
+      </c>
       <c r="BO10" t="n">
-        <v>1.702</v>
+        <v>3.405</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.405</v>
+        <v>0.54</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.54</v>
+        <v>0.374</v>
       </c>
       <c r="BR10" t="n">
-        <v>0.374</v>
+        <v>32.954</v>
       </c>
       <c r="BS10" t="n">
-        <v>32.954</v>
+        <v>21.619</v>
       </c>
       <c r="BT10" t="n">
-        <v>21.619</v>
-      </c>
-      <c r="BU10" t="n">
         <v>3.388</v>
       </c>
     </row>
@@ -2919,229 +2869,224 @@
       <c r="B11" t="b">
         <v>0</v>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>5280x3956</t>
-        </is>
+      <c r="C11" t="n">
+        <v>147.25</v>
       </c>
       <c r="D11" t="n">
-        <v>147.25</v>
+        <v>132.175</v>
       </c>
       <c r="E11" t="n">
-        <v>132.175</v>
+        <v>107.642</v>
       </c>
       <c r="F11" t="n">
-        <v>107.642</v>
+        <v>27.545</v>
       </c>
       <c r="G11" t="n">
-        <v>27.545</v>
+        <v>18.577</v>
       </c>
       <c r="H11" t="n">
-        <v>18.577</v>
-      </c>
-      <c r="I11" t="n">
         <v>18.293</v>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
+      <c r="J11" t="n">
+        <v>0.614</v>
+      </c>
       <c r="K11" t="n">
-        <v>0.614</v>
+        <v>1.037</v>
       </c>
       <c r="L11" t="n">
-        <v>1.037</v>
+        <v>1.228</v>
       </c>
       <c r="M11" t="n">
-        <v>1.228</v>
+        <v>0.77</v>
       </c>
       <c r="N11" t="n">
-        <v>0.77</v>
+        <v>21.472</v>
       </c>
       <c r="O11" t="n">
-        <v>21.472</v>
+        <v>108.789</v>
       </c>
       <c r="P11" t="n">
-        <v>108.789</v>
+        <v>6.36</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.36</v>
+        <v>130.906</v>
       </c>
       <c r="R11" t="n">
-        <v>130.906</v>
+        <v>124.395</v>
       </c>
       <c r="S11" t="n">
-        <v>124.395</v>
+        <v>103.397</v>
       </c>
       <c r="T11" t="n">
-        <v>103.397</v>
+        <v>17.008</v>
       </c>
       <c r="U11" t="n">
-        <v>17.008</v>
+        <v>14.456</v>
       </c>
       <c r="V11" t="n">
-        <v>14.456</v>
-      </c>
-      <c r="W11" t="n">
         <v>15.536</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
+      <c r="X11" t="n">
+        <v>0.575</v>
+      </c>
       <c r="Y11" t="n">
-        <v>0.575</v>
+        <v>1.062</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.062</v>
+        <v>1.149</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.149</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8100000000000001</v>
+        <v>15.667</v>
       </c>
       <c r="AC11" t="n">
-        <v>15.667</v>
+        <v>141.91</v>
       </c>
       <c r="AD11" t="n">
-        <v>141.91</v>
+        <v>5.983</v>
       </c>
       <c r="AE11" t="n">
-        <v>5.983</v>
+        <v>156.489</v>
       </c>
       <c r="AF11" t="n">
-        <v>156.489</v>
+        <v>138.303</v>
       </c>
       <c r="AG11" t="n">
-        <v>138.303</v>
+        <v>110.859</v>
       </c>
       <c r="AH11" t="n">
-        <v>110.859</v>
+        <v>24.002</v>
       </c>
       <c r="AI11" t="n">
-        <v>24.002</v>
+        <v>15.651</v>
       </c>
       <c r="AJ11" t="n">
-        <v>15.651</v>
-      </c>
-      <c r="AK11" t="n">
         <v>18.489</v>
       </c>
-      <c r="AL11" t="inlineStr">
+      <c r="AK11" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
+      <c r="AL11" t="n">
+        <v>0.628</v>
+      </c>
       <c r="AM11" t="n">
-        <v>0.628</v>
+        <v>1.035</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.035</v>
+        <v>1.256</v>
       </c>
       <c r="AO11" t="n">
-        <v>1.256</v>
+        <v>0.752</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.752</v>
+        <v>19.381</v>
       </c>
       <c r="AQ11" t="n">
-        <v>19.381</v>
+        <v>118.556</v>
       </c>
       <c r="AR11" t="n">
-        <v>118.556</v>
+        <v>6.201</v>
       </c>
       <c r="AS11" t="n">
-        <v>6.201</v>
+        <v>143.76</v>
       </c>
       <c r="AT11" t="n">
-        <v>143.76</v>
+        <v>135.407</v>
       </c>
       <c r="AU11" t="n">
-        <v>135.407</v>
+        <v>110.214</v>
       </c>
       <c r="AV11" t="n">
-        <v>110.214</v>
+        <v>22.262</v>
       </c>
       <c r="AW11" t="n">
-        <v>22.262</v>
+        <v>16.205</v>
       </c>
       <c r="AX11" t="n">
-        <v>16.205</v>
-      </c>
-      <c r="AY11" t="n">
         <v>16.721</v>
       </c>
-      <c r="AZ11" t="inlineStr">
+      <c r="AY11" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
+      <c r="AZ11" t="n">
+        <v>0.585</v>
+      </c>
       <c r="BA11" t="n">
-        <v>0.585</v>
+        <v>1.066</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.066</v>
+        <v>1.171</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.171</v>
+        <v>0.79</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.79</v>
+        <v>18.396</v>
       </c>
       <c r="BE11" t="n">
-        <v>18.396</v>
+        <v>120.906</v>
       </c>
       <c r="BF11" t="n">
-        <v>120.906</v>
+        <v>6.138</v>
       </c>
       <c r="BG11" t="n">
-        <v>6.138</v>
+        <v>144.601</v>
       </c>
       <c r="BH11" t="n">
-        <v>144.601</v>
+        <v>132.57</v>
       </c>
       <c r="BI11" t="n">
-        <v>132.57</v>
+        <v>108.028</v>
       </c>
       <c r="BJ11" t="n">
-        <v>108.028</v>
+        <v>24.781</v>
       </c>
       <c r="BK11" t="n">
-        <v>24.781</v>
+        <v>17.099</v>
       </c>
       <c r="BL11" t="n">
-        <v>17.099</v>
-      </c>
-      <c r="BM11" t="n">
         <v>17.549</v>
       </c>
-      <c r="BN11" t="inlineStr">
+      <c r="BM11" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
+      <c r="BN11" t="n">
+        <v>0.601</v>
+      </c>
       <c r="BO11" t="n">
-        <v>0.601</v>
+        <v>1.05</v>
       </c>
       <c r="BP11" t="n">
-        <v>1.05</v>
+        <v>1.202</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.202</v>
+        <v>0.78</v>
       </c>
       <c r="BR11" t="n">
-        <v>0.78</v>
+        <v>19.809</v>
       </c>
       <c r="BS11" t="n">
-        <v>19.809</v>
+        <v>122.402</v>
       </c>
       <c r="BT11" t="n">
-        <v>122.402</v>
-      </c>
-      <c r="BU11" t="n">
         <v>6.269</v>
       </c>
     </row>
@@ -3154,229 +3099,224 @@
       <c r="B12" t="b">
         <v>0</v>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>5280x3956</t>
-        </is>
+      <c r="C12" t="n">
+        <v>142.14</v>
       </c>
       <c r="D12" t="n">
-        <v>142.14</v>
+        <v>128.108</v>
       </c>
       <c r="E12" t="n">
-        <v>128.108</v>
+        <v>105.668</v>
       </c>
       <c r="F12" t="n">
-        <v>105.668</v>
+        <v>25.716</v>
       </c>
       <c r="G12" t="n">
-        <v>25.716</v>
+        <v>17.718</v>
       </c>
       <c r="H12" t="n">
-        <v>17.718</v>
-      </c>
-      <c r="I12" t="n">
         <v>17.086</v>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
+      <c r="J12" t="n">
+        <v>0.608</v>
+      </c>
       <c r="K12" t="n">
-        <v>0.608</v>
+        <v>1.034</v>
       </c>
       <c r="L12" t="n">
-        <v>1.034</v>
+        <v>1.216</v>
       </c>
       <c r="M12" t="n">
-        <v>1.216</v>
+        <v>0.782</v>
       </c>
       <c r="N12" t="n">
-        <v>0.782</v>
+        <v>20.173</v>
       </c>
       <c r="O12" t="n">
-        <v>20.173</v>
+        <v>108.966</v>
       </c>
       <c r="P12" t="n">
-        <v>108.966</v>
+        <v>6.229</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.229</v>
+        <v>130.249</v>
       </c>
       <c r="R12" t="n">
-        <v>130.249</v>
+        <v>123.105</v>
       </c>
       <c r="S12" t="n">
-        <v>123.105</v>
+        <v>103.641</v>
       </c>
       <c r="T12" t="n">
-        <v>103.641</v>
+        <v>16.295</v>
       </c>
       <c r="U12" t="n">
-        <v>16.295</v>
+        <v>13.7</v>
       </c>
       <c r="V12" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="W12" t="n">
         <v>14.916</v>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
+      <c r="X12" t="n">
+        <v>0.574</v>
+      </c>
       <c r="Y12" t="n">
-        <v>0.574</v>
+        <v>1.053</v>
       </c>
       <c r="Z12" t="n">
+        <v>1.149</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.8179999999999999</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>14.97</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>132.55</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>5.922</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>153.587</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>137.676</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>110.09</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>26.59</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>17.202</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>19.34</v>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="AL12" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.044</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0.756</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>21.044</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>115.565</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>6.335</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>135.55</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>130.22</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>105.098</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>18.891</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>15.486</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>16.304</v>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0.576</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>1.082</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1.152</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>16.894</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>119.369</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>6.066</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>140.382</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>129.777</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>106.124</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>23.949</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>16.935</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>17.157</v>
+      </c>
+      <c r="BM12" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="BN12" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="BO12" t="n">
         <v>1.053</v>
       </c>
-      <c r="AA12" t="n">
-        <v>1.149</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>0.8179999999999999</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>14.97</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>132.55</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>5.922</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>153.587</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>137.676</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>110.09</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>26.59</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>17.202</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>19.34</v>
-      </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="AM12" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>1.044</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>0.756</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>21.044</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>115.565</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>6.335</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>135.55</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>130.22</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>105.098</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>18.891</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>15.486</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>16.304</v>
-      </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="BA12" t="n">
-        <v>0.576</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>1.082</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>1.152</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>0.791</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>16.894</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>119.369</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>6.066</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>140.382</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>129.777</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>106.124</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>23.949</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>16.935</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>17.157</v>
-      </c>
-      <c r="BN12" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="BO12" t="n">
-        <v>0.595</v>
-      </c>
       <c r="BP12" t="n">
-        <v>1.053</v>
+        <v>1.19</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1.19</v>
+        <v>0.786</v>
       </c>
       <c r="BR12" t="n">
-        <v>0.786</v>
+        <v>19.347</v>
       </c>
       <c r="BS12" t="n">
-        <v>19.347</v>
+        <v>118.963</v>
       </c>
       <c r="BT12" t="n">
-        <v>118.963</v>
-      </c>
-      <c r="BU12" t="n">
         <v>6.232</v>
       </c>
     </row>
@@ -3389,10 +3329,8 @@
       <c r="B13" t="b">
         <v>1</v>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1536x648</t>
-        </is>
+      <c r="C13" t="n">
+        <v>0</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -3409,14 +3347,14 @@
       <c r="H13" t="n">
         <v>0</v>
       </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
@@ -3433,165 +3371,165 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
         <v>-0</v>
       </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="n">
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
         <v>-0</v>
       </c>
-      <c r="AF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL13" t="inlineStr">
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="AM13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS13" t="n">
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF13" t="n">
         <v>-0</v>
       </c>
-      <c r="AT13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ13" t="inlineStr">
+      <c r="BG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM13" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="BA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>-0</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN13" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
+      <c r="BN13" t="n">
+        <v>0</v>
       </c>
       <c r="BO13" t="n">
         <v>0</v>
@@ -3609,9 +3547,6 @@
         <v>0</v>
       </c>
       <c r="BT13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU13" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -3624,229 +3559,224 @@
       <c r="B14" t="b">
         <v>1</v>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>5472x3648</t>
-        </is>
+      <c r="C14" t="n">
+        <v>85.84399999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>85.84399999999999</v>
+        <v>182.645</v>
       </c>
       <c r="E14" t="n">
-        <v>182.645</v>
+        <v>48.915</v>
       </c>
       <c r="F14" t="n">
-        <v>48.915</v>
+        <v>63.727</v>
       </c>
       <c r="G14" t="n">
-        <v>63.727</v>
+        <v>51.262</v>
       </c>
       <c r="H14" t="n">
-        <v>51.262</v>
-      </c>
-      <c r="I14" t="n">
         <v>45.429</v>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
+      <c r="J14" t="n">
+        <v>1.355</v>
+      </c>
       <c r="K14" t="n">
-        <v>1.355</v>
+        <v>2.711</v>
       </c>
       <c r="L14" t="n">
-        <v>2.711</v>
+        <v>0.741</v>
       </c>
       <c r="M14" t="n">
-        <v>0.741</v>
+        <v>0.364</v>
       </c>
       <c r="N14" t="n">
-        <v>0.364</v>
+        <v>53.473</v>
       </c>
       <c r="O14" t="n">
-        <v>53.473</v>
+        <v>8759.894</v>
       </c>
       <c r="P14" t="n">
-        <v>8759.894</v>
+        <v>4.316</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.316</v>
+        <v>70.836</v>
       </c>
       <c r="R14" t="n">
-        <v>70.836</v>
+        <v>176.154</v>
       </c>
       <c r="S14" t="n">
-        <v>176.154</v>
+        <v>35.308</v>
       </c>
       <c r="T14" t="n">
-        <v>35.308</v>
+        <v>44.647</v>
       </c>
       <c r="U14" t="n">
-        <v>44.647</v>
+        <v>54.111</v>
       </c>
       <c r="V14" t="n">
-        <v>54.111</v>
-      </c>
-      <c r="W14" t="n">
         <v>26.501</v>
       </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
+      <c r="X14" t="n">
+        <v>1.66</v>
+      </c>
       <c r="Y14" t="n">
-        <v>1.66</v>
+        <v>3.319</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.319</v>
+        <v>0.67</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.67</v>
+        <v>0.286</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.286</v>
+        <v>41.753</v>
       </c>
       <c r="AC14" t="n">
-        <v>41.753</v>
+        <v>8449.906999999999</v>
       </c>
       <c r="AD14" t="n">
-        <v>8449.906999999999</v>
+        <v>4.1</v>
       </c>
       <c r="AE14" t="n">
-        <v>4.1</v>
+        <v>143.664</v>
       </c>
       <c r="AF14" t="n">
-        <v>143.664</v>
+        <v>154.577</v>
       </c>
       <c r="AG14" t="n">
-        <v>154.577</v>
+        <v>92.747</v>
       </c>
       <c r="AH14" t="n">
-        <v>92.747</v>
+        <v>42.064</v>
       </c>
       <c r="AI14" t="n">
-        <v>42.064</v>
+        <v>19.571</v>
       </c>
       <c r="AJ14" t="n">
-        <v>19.571</v>
-      </c>
-      <c r="AK14" t="n">
         <v>34.653</v>
       </c>
-      <c r="AL14" t="inlineStr">
+      <c r="AK14" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
+      <c r="AL14" t="n">
+        <v>0.654</v>
+      </c>
       <c r="AM14" t="n">
-        <v>0.654</v>
+        <v>1.308</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.308</v>
+        <v>1.162</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.162</v>
+        <v>0.622</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.622</v>
+        <v>32.096</v>
       </c>
       <c r="AQ14" t="n">
-        <v>32.096</v>
+        <v>75.923</v>
       </c>
       <c r="AR14" t="n">
-        <v>75.923</v>
+        <v>6.528</v>
       </c>
       <c r="AS14" t="n">
-        <v>6.528</v>
+        <v>103.5</v>
       </c>
       <c r="AT14" t="n">
-        <v>103.5</v>
+        <v>137.428</v>
       </c>
       <c r="AU14" t="n">
-        <v>137.428</v>
+        <v>57.253</v>
       </c>
       <c r="AV14" t="n">
-        <v>57.253</v>
+        <v>14.993</v>
       </c>
       <c r="AW14" t="n">
-        <v>14.993</v>
+        <v>15.501</v>
       </c>
       <c r="AX14" t="n">
-        <v>15.501</v>
-      </c>
-      <c r="AY14" t="n">
         <v>13.1</v>
       </c>
-      <c r="AZ14" t="inlineStr">
+      <c r="AY14" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
+      <c r="AZ14" t="n">
+        <v>0.855</v>
+      </c>
       <c r="BA14" t="n">
-        <v>0.855</v>
+        <v>1.71</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.71</v>
+        <v>1.063</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.063</v>
+        <v>0.475</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.475</v>
+        <v>14.531</v>
       </c>
       <c r="BE14" t="n">
-        <v>14.531</v>
+        <v>82.16</v>
       </c>
       <c r="BF14" t="n">
-        <v>82.16</v>
+        <v>5.861</v>
       </c>
       <c r="BG14" t="n">
-        <v>5.861</v>
+        <v>100.961</v>
       </c>
       <c r="BH14" t="n">
-        <v>100.961</v>
+        <v>162.701</v>
       </c>
       <c r="BI14" t="n">
-        <v>162.701</v>
+        <v>58.556</v>
       </c>
       <c r="BJ14" t="n">
-        <v>58.556</v>
+        <v>52.475</v>
       </c>
       <c r="BK14" t="n">
-        <v>52.475</v>
+        <v>43.193</v>
       </c>
       <c r="BL14" t="n">
-        <v>43.193</v>
-      </c>
-      <c r="BM14" t="n">
         <v>38.544</v>
       </c>
-      <c r="BN14" t="inlineStr">
+      <c r="BM14" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
+      <c r="BN14" t="n">
+        <v>1.02</v>
+      </c>
       <c r="BO14" t="n">
-        <v>1.02</v>
+        <v>2.04</v>
       </c>
       <c r="BP14" t="n">
-        <v>2.04</v>
+        <v>0.913</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0.913</v>
+        <v>0.444</v>
       </c>
       <c r="BR14" t="n">
-        <v>0.444</v>
+        <v>44.738</v>
       </c>
       <c r="BS14" t="n">
-        <v>44.738</v>
+        <v>4340.768</v>
       </c>
       <c r="BT14" t="n">
-        <v>4340.768</v>
-      </c>
-      <c r="BU14" t="n">
         <v>5.749</v>
       </c>
     </row>

--- a/photo_analyzer/analysis_report.xlsx
+++ b/photo_analyzer/analysis_report.xlsx
@@ -800,30 +800,30 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>116.081</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>115.653</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>94.907</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>31.025</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>23.649</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>32.778</v>
+        <v>0</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0.551</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>1.096</v>
@@ -838,36 +838,36 @@
         <v>29.151</v>
       </c>
       <c r="O2" t="n">
-        <v>171.667</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
         <v>6.773</v>
       </c>
       <c r="Q2" t="n">
-        <v>123.551</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>117.81</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>106.542</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>19.088</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>17.346</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>19.534</v>
+        <v>0</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>0.551</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
         <v>1.024</v>
@@ -882,36 +882,36 @@
         <v>18.656</v>
       </c>
       <c r="AC2" t="n">
-        <v>137.538</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
         <v>6.236</v>
       </c>
       <c r="AE2" t="n">
-        <v>106.728</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>113.287</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>78.212</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>34.42</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>28.161</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>35.879</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="AL2" t="n">
-        <v>0.613</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
         <v>1.225</v>
@@ -926,36 +926,36 @@
         <v>32.82</v>
       </c>
       <c r="AQ2" t="n">
-        <v>355.8</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
         <v>7.025</v>
       </c>
       <c r="AS2" t="n">
-        <v>126.599</v>
+        <v>0</v>
       </c>
       <c r="AT2" t="n">
-        <v>124.712</v>
+        <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>105.024</v>
+        <v>0</v>
       </c>
       <c r="AV2" t="n">
-        <v>32.512</v>
+        <v>0</v>
       </c>
       <c r="AW2" t="n">
-        <v>26.247</v>
+        <v>0</v>
       </c>
       <c r="AX2" t="n">
-        <v>33.565</v>
+        <v>0</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>0.551</v>
+        <v>0</v>
       </c>
       <c r="BA2" t="n">
         <v>1.077</v>
@@ -970,36 +970,36 @@
         <v>30.775</v>
       </c>
       <c r="BE2" t="n">
-        <v>136.589</v>
+        <v>0</v>
       </c>
       <c r="BF2" t="n">
         <v>6.898</v>
       </c>
       <c r="BG2" t="n">
-        <v>118.239</v>
+        <v>0</v>
       </c>
       <c r="BH2" t="n">
-        <v>117.866</v>
+        <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>96.17100000000001</v>
+        <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>30.838</v>
+        <v>0</v>
       </c>
       <c r="BK2" t="n">
-        <v>24.571</v>
+        <v>0</v>
       </c>
       <c r="BL2" t="n">
-        <v>33.091</v>
+        <v>0</v>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="BN2" t="n">
-        <v>0.552</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
         <v>1.099</v>
@@ -1014,7 +1014,7 @@
         <v>29.5</v>
       </c>
       <c r="BS2" t="n">
-        <v>200.203</v>
+        <v>0</v>
       </c>
       <c r="BT2" t="n">
         <v>6.859</v>
@@ -1030,30 +1030,30 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>126.126</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>126.519</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>125.265</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>11.29</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>9.606</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>14.542</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0.503</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
         <v>1.007</v>
@@ -1068,36 +1068,36 @@
         <v>11.813</v>
       </c>
       <c r="O3" t="n">
-        <v>24.012</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
         <v>0.602</v>
       </c>
       <c r="Q3" t="n">
-        <v>127.477</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>127.264</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>126.85</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>3.626</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>4.197</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>6.215</v>
+        <v>0</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>0.502</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
         <v>1.001</v>
@@ -1112,19 +1112,19 @@
         <v>4.679</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.011</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
         <v>0.473</v>
       </c>
       <c r="AE3" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
         <v>0</v>
@@ -1137,11 +1137,11 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="AL3" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
         <v>1</v>
@@ -1162,13 +1162,13 @@
         <v>-0</v>
       </c>
       <c r="AS3" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
@@ -1181,11 +1181,11 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="BA3" t="n">
         <v>1</v>
@@ -1206,30 +1206,30 @@
         <v>-0</v>
       </c>
       <c r="BG3" t="n">
-        <v>127.401</v>
+        <v>0</v>
       </c>
       <c r="BH3" t="n">
-        <v>127.446</v>
+        <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>127.029</v>
+        <v>0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>5.979</v>
+        <v>0</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.277</v>
+        <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>7.986</v>
+        <v>0</v>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="BN3" t="n">
-        <v>0.501</v>
+        <v>0</v>
       </c>
       <c r="BO3" t="n">
         <v>1.002</v>
@@ -1244,7 +1244,7 @@
         <v>6.414</v>
       </c>
       <c r="BS3" t="n">
-        <v>6.755</v>
+        <v>0</v>
       </c>
       <c r="BT3" t="n">
         <v>0.3</v>
@@ -1260,30 +1260,30 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>122.398</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>123.434</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>121.243</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>18.239</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>15.265</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>21.395</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.507</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
         <v>1.013</v>
@@ -1298,36 +1298,36 @@
         <v>18.3</v>
       </c>
       <c r="O4" t="n">
-        <v>20.117</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>1.076</v>
       </c>
       <c r="Q4" t="n">
-        <v>126.441</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>126.006</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>124.863</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>9.403</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>9.148</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>12.617</v>
+        <v>0</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>0.504</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
         <v>1.003</v>
@@ -1342,19 +1342,19 @@
         <v>10.389</v>
       </c>
       <c r="AC4" t="n">
-        <v>11.787</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
         <v>1.006</v>
       </c>
       <c r="AE4" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
         <v>0</v>
@@ -1367,11 +1367,11 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="AL4" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
         <v>1</v>
@@ -1392,13 +1392,13 @@
         <v>-0</v>
       </c>
       <c r="AS4" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="AV4" t="n">
         <v>0</v>
@@ -1411,11 +1411,11 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="BA4" t="n">
         <v>1</v>
@@ -1436,30 +1436,30 @@
         <v>-0</v>
       </c>
       <c r="BG4" t="n">
-        <v>126.21</v>
+        <v>0</v>
       </c>
       <c r="BH4" t="n">
-        <v>126.36</v>
+        <v>0</v>
       </c>
       <c r="BI4" t="n">
-        <v>125.527</v>
+        <v>0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>10.513</v>
+        <v>0</v>
       </c>
       <c r="BK4" t="n">
-        <v>9.093</v>
+        <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>12.727</v>
+        <v>0</v>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="BN4" t="n">
-        <v>0.502</v>
+        <v>0</v>
       </c>
       <c r="BO4" t="n">
         <v>1.004</v>
@@ -1474,7 +1474,7 @@
         <v>10.778</v>
       </c>
       <c r="BS4" t="n">
-        <v>7.974</v>
+        <v>0</v>
       </c>
       <c r="BT4" t="n">
         <v>0.589</v>
@@ -1490,30 +1490,30 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>119.572</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>122.236</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>116.218</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>20.464</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>15.947</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>26.197</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0.518</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>1.037</v>
@@ -1528,36 +1528,36 @@
         <v>20.869</v>
       </c>
       <c r="O5" t="n">
-        <v>55.915</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>1.914</v>
       </c>
       <c r="Q5" t="n">
-        <v>124.055</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>123.95</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>120.61</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>18.994</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>15.141</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>21.429</v>
+        <v>0</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>0.507</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
         <v>1.013</v>
@@ -1572,19 +1572,19 @@
         <v>18.522</v>
       </c>
       <c r="AC5" t="n">
-        <v>29.586</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
         <v>1.939</v>
       </c>
       <c r="AE5" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
         <v>0</v>
@@ -1597,11 +1597,11 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="AL5" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
         <v>1</v>
@@ -1622,13 +1622,13 @@
         <v>-0</v>
       </c>
       <c r="AS5" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="AV5" t="n">
         <v>0</v>
@@ -1641,11 +1641,11 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="BA5" t="n">
         <v>1</v>
@@ -1666,30 +1666,30 @@
         <v>-0</v>
       </c>
       <c r="BG5" t="n">
-        <v>124.907</v>
+        <v>0</v>
       </c>
       <c r="BH5" t="n">
-        <v>125.546</v>
+        <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>123.207</v>
+        <v>0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>14.386</v>
+        <v>0</v>
       </c>
       <c r="BK5" t="n">
-        <v>11.282</v>
+        <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>17.657</v>
+        <v>0</v>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="BN5" t="n">
-        <v>0.506</v>
+        <v>0</v>
       </c>
       <c r="BO5" t="n">
         <v>1.012</v>
@@ -1704,7 +1704,7 @@
         <v>14.442</v>
       </c>
       <c r="BS5" t="n">
-        <v>21.358</v>
+        <v>0</v>
       </c>
       <c r="BT5" t="n">
         <v>1.082</v>
@@ -1720,30 +1720,30 @@
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>121.91</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>124.442</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>119.413</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>20.885</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>13.97</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>24.579</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>0.516</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>1.031</v>
@@ -1758,36 +1758,36 @@
         <v>19.812</v>
       </c>
       <c r="O6" t="n">
-        <v>50.078</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>1.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>122.776</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>124.386</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>120.623</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>21.599</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>15.081</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>23.799</v>
+        <v>0</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>0.511</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
         <v>1.022</v>
@@ -1802,19 +1802,19 @@
         <v>20.159</v>
       </c>
       <c r="AC6" t="n">
-        <v>36.239</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
         <v>1.475</v>
       </c>
       <c r="AE6" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
         <v>0</v>
@@ -1827,11 +1827,11 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="AL6" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AM6" t="n">
         <v>1</v>
@@ -1852,13 +1852,13 @@
         <v>-0</v>
       </c>
       <c r="AS6" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
@@ -1871,11 +1871,11 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="BA6" t="n">
         <v>1</v>
@@ -1896,30 +1896,30 @@
         <v>-0</v>
       </c>
       <c r="BG6" t="n">
-        <v>125.172</v>
+        <v>0</v>
       </c>
       <c r="BH6" t="n">
-        <v>126.207</v>
+        <v>0</v>
       </c>
       <c r="BI6" t="n">
-        <v>124.009</v>
+        <v>0</v>
       </c>
       <c r="BJ6" t="n">
-        <v>15.29</v>
+        <v>0</v>
       </c>
       <c r="BK6" t="n">
-        <v>10.434</v>
+        <v>0</v>
       </c>
       <c r="BL6" t="n">
-        <v>17.571</v>
+        <v>0</v>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="BN6" t="n">
-        <v>0.506</v>
+        <v>0</v>
       </c>
       <c r="BO6" t="n">
         <v>1.013</v>
@@ -1934,7 +1934,7 @@
         <v>14.431</v>
       </c>
       <c r="BS6" t="n">
-        <v>21.566</v>
+        <v>0</v>
       </c>
       <c r="BT6" t="n">
         <v>0.819</v>
@@ -1950,30 +1950,30 @@
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>113.795</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>117.904</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>110.991</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>45.006</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>33.685</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>43.229</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>0.525</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>1.049</v>
@@ -1988,36 +1988,36 @@
         <v>40.64</v>
       </c>
       <c r="O7" t="n">
-        <v>46.392</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>1.903</v>
       </c>
       <c r="Q7" t="n">
-        <v>110.218</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>115.929</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>108.817</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>42.329</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>30.676</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>42.976</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>0.529</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
         <v>1.059</v>
@@ -2032,19 +2032,19 @@
         <v>38.66</v>
       </c>
       <c r="AC7" t="n">
-        <v>59.734</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
         <v>1.732</v>
       </c>
       <c r="AE7" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
         <v>0</v>
@@ -2057,11 +2057,11 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="AL7" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
         <v>1</v>
@@ -2082,13 +2082,13 @@
         <v>-0</v>
       </c>
       <c r="AS7" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="AT7" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -2101,11 +2101,11 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="BA7" t="n">
         <v>1</v>
@@ -2126,30 +2126,30 @@
         <v>-0</v>
       </c>
       <c r="BG7" t="n">
-        <v>120.003</v>
+        <v>0</v>
       </c>
       <c r="BH7" t="n">
-        <v>122.458</v>
+        <v>0</v>
       </c>
       <c r="BI7" t="n">
-        <v>118.952</v>
+        <v>0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>31.935</v>
+        <v>0</v>
       </c>
       <c r="BK7" t="n">
-        <v>23.455</v>
+        <v>0</v>
       </c>
       <c r="BL7" t="n">
-        <v>31.802</v>
+        <v>0</v>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="BN7" t="n">
-        <v>0.512</v>
+        <v>0</v>
       </c>
       <c r="BO7" t="n">
         <v>1.025</v>
@@ -2164,7 +2164,7 @@
         <v>29.064</v>
       </c>
       <c r="BS7" t="n">
-        <v>26.518</v>
+        <v>0</v>
       </c>
       <c r="BT7" t="n">
         <v>1.029</v>
@@ -2180,30 +2180,30 @@
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>126.369</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>127.251</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>124.511</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>15.2</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>11.429</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>15.984</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>0.507</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>1.014</v>
@@ -2218,36 +2218,36 @@
         <v>14.204</v>
       </c>
       <c r="O8" t="n">
-        <v>27.89</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>0.991</v>
       </c>
       <c r="Q8" t="n">
-        <v>127.569</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>127.886</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>126.124</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>13.632</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>10.086</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>13.63</v>
+        <v>0</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>0.504</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
         <v>1.008</v>
@@ -2262,19 +2262,19 @@
         <v>12.45</v>
       </c>
       <c r="AC8" t="n">
-        <v>17.574</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
         <v>0.9</v>
       </c>
       <c r="AE8" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
         <v>0</v>
@@ -2287,11 +2287,11 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="AL8" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
         <v>1</v>
@@ -2312,13 +2312,13 @@
         <v>-0</v>
       </c>
       <c r="AS8" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="AV8" t="n">
         <v>0</v>
@@ -2331,11 +2331,11 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="BA8" t="n">
         <v>1</v>
@@ -2356,30 +2356,30 @@
         <v>-0</v>
       </c>
       <c r="BG8" t="n">
-        <v>127.484</v>
+        <v>0</v>
       </c>
       <c r="BH8" t="n">
-        <v>127.784</v>
+        <v>0</v>
       </c>
       <c r="BI8" t="n">
-        <v>126.659</v>
+        <v>0</v>
       </c>
       <c r="BJ8" t="n">
-        <v>10.23</v>
+        <v>0</v>
       </c>
       <c r="BK8" t="n">
-        <v>7.628</v>
+        <v>0</v>
       </c>
       <c r="BL8" t="n">
-        <v>10.604</v>
+        <v>0</v>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="BN8" t="n">
-        <v>0.503</v>
+        <v>0</v>
       </c>
       <c r="BO8" t="n">
         <v>1.006</v>
@@ -2394,7 +2394,7 @@
         <v>9.487</v>
       </c>
       <c r="BS8" t="n">
-        <v>11.355</v>
+        <v>0</v>
       </c>
       <c r="BT8" t="n">
         <v>0.519</v>
@@ -2410,30 +2410,30 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>109.017</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>121.814</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>83.931</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>48.555</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>40.157</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>39.052</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>0.631</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>1.263</v>
@@ -2448,36 +2448,36 @@
         <v>42.588</v>
       </c>
       <c r="O9" t="n">
-        <v>620.151</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
         <v>7.315</v>
       </c>
       <c r="Q9" t="n">
-        <v>132.633</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>136.04</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>107.792</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>51.106</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>38.355</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>47.487</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>0.5659999999999999</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
         <v>1.132</v>
@@ -2492,36 +2492,36 @@
         <v>45.649</v>
       </c>
       <c r="AC9" t="n">
-        <v>413.589</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
         <v>7.346</v>
       </c>
       <c r="AE9" t="n">
-        <v>109.962</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>125.55</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>80.771</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>50.019</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>41.6</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>40.593</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="AL9" t="n">
-        <v>0.658</v>
+        <v>0</v>
       </c>
       <c r="AM9" t="n">
         <v>1.317</v>
@@ -2536,36 +2536,36 @@
         <v>44.071</v>
       </c>
       <c r="AQ9" t="n">
-        <v>754.211</v>
+        <v>0</v>
       </c>
       <c r="AR9" t="n">
         <v>7.401</v>
       </c>
       <c r="AS9" t="n">
-        <v>136.668</v>
+        <v>0</v>
       </c>
       <c r="AT9" t="n">
-        <v>143.008</v>
+        <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>109.931</v>
+        <v>0</v>
       </c>
       <c r="AV9" t="n">
-        <v>51.51</v>
+        <v>0</v>
       </c>
       <c r="AW9" t="n">
-        <v>37.857</v>
+        <v>0</v>
       </c>
       <c r="AX9" t="n">
-        <v>49.072</v>
+        <v>0</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>0.58</v>
+        <v>0</v>
       </c>
       <c r="BA9" t="n">
         <v>1.16</v>
@@ -2580,36 +2580,36 @@
         <v>46.147</v>
       </c>
       <c r="BE9" t="n">
-        <v>317.733</v>
+        <v>0</v>
       </c>
       <c r="BF9" t="n">
         <v>7.26</v>
       </c>
       <c r="BG9" t="n">
-        <v>122.07</v>
+        <v>0</v>
       </c>
       <c r="BH9" t="n">
-        <v>131.603</v>
+        <v>0</v>
       </c>
       <c r="BI9" t="n">
-        <v>95.60599999999999</v>
+        <v>0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>51.88</v>
+        <v>0</v>
       </c>
       <c r="BK9" t="n">
-        <v>40.403</v>
+        <v>0</v>
       </c>
       <c r="BL9" t="n">
-        <v>46.222</v>
+        <v>0</v>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="BN9" t="n">
-        <v>0.605</v>
+        <v>0</v>
       </c>
       <c r="BO9" t="n">
         <v>1.209</v>
@@ -2624,7 +2624,7 @@
         <v>46.169</v>
       </c>
       <c r="BS9" t="n">
-        <v>525.857</v>
+        <v>0</v>
       </c>
       <c r="BT9" t="n">
         <v>7.487</v>
@@ -2640,30 +2640,30 @@
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>31.213</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>53.255</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>22.408</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>58.037</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>37.763</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>41.378</v>
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>0.993</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>1.986</v>
@@ -2678,36 +2678,36 @@
         <v>45.726</v>
       </c>
       <c r="O10" t="n">
-        <v>42.939</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
         <v>4.161</v>
       </c>
       <c r="Q10" t="n">
-        <v>27.192</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>52.583</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>20.6</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>50.801</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>33.561</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>38.577</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
         <v>2.201</v>
@@ -2722,36 +2722,36 @@
         <v>40.979</v>
       </c>
       <c r="AC10" t="n">
-        <v>35.757</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
         <v>3.297</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>32.345</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.034</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.419</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>4.194</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.628</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="AL10" t="n">
-        <v>737.229</v>
+        <v>0</v>
       </c>
       <c r="AM10" t="n">
         <v>1474.457</v>
@@ -2766,36 +2766,36 @@
         <v>1.747</v>
       </c>
       <c r="AQ10" t="n">
-        <v>2.287</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
         <v>2.218</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.153</v>
+        <v>0</v>
       </c>
       <c r="AT10" t="n">
-        <v>35.475</v>
+        <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.399</v>
+        <v>0</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.613</v>
+        <v>0</v>
       </c>
       <c r="AW10" t="n">
-        <v>7.087</v>
+        <v>0</v>
       </c>
       <c r="AX10" t="n">
-        <v>3.476</v>
+        <v>0</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>64.246</v>
+        <v>0</v>
       </c>
       <c r="BA10" t="n">
         <v>128.491</v>
@@ -2810,36 +2810,36 @@
         <v>4.059</v>
       </c>
       <c r="BE10" t="n">
-        <v>5.528</v>
+        <v>0</v>
       </c>
       <c r="BF10" t="n">
         <v>2.473</v>
       </c>
       <c r="BG10" t="n">
-        <v>14.642</v>
+        <v>0</v>
       </c>
       <c r="BH10" t="n">
-        <v>43.415</v>
+        <v>0</v>
       </c>
       <c r="BI10" t="n">
-        <v>10.86</v>
+        <v>0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>41.255</v>
+        <v>0</v>
       </c>
       <c r="BK10" t="n">
-        <v>27.325</v>
+        <v>0</v>
       </c>
       <c r="BL10" t="n">
-        <v>30.281</v>
+        <v>0</v>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="BN10" t="n">
-        <v>1.702</v>
+        <v>0</v>
       </c>
       <c r="BO10" t="n">
         <v>3.405</v>
@@ -2854,7 +2854,7 @@
         <v>32.954</v>
       </c>
       <c r="BS10" t="n">
-        <v>21.619</v>
+        <v>0</v>
       </c>
       <c r="BT10" t="n">
         <v>3.388</v>
@@ -2870,30 +2870,30 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>147.25</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>132.175</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>107.642</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>27.545</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>18.577</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>18.293</v>
+        <v>0</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>0.614</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>1.037</v>
@@ -2908,36 +2908,36 @@
         <v>21.472</v>
       </c>
       <c r="O11" t="n">
-        <v>108.789</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
         <v>6.36</v>
       </c>
       <c r="Q11" t="n">
-        <v>130.906</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>124.395</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>103.397</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>17.008</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>14.456</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>15.536</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>0.575</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
         <v>1.062</v>
@@ -2952,36 +2952,36 @@
         <v>15.667</v>
       </c>
       <c r="AC11" t="n">
-        <v>141.91</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
         <v>5.983</v>
       </c>
       <c r="AE11" t="n">
-        <v>156.489</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>138.303</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>110.859</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>24.002</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>15.651</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>18.489</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="AL11" t="n">
-        <v>0.628</v>
+        <v>0</v>
       </c>
       <c r="AM11" t="n">
         <v>1.035</v>
@@ -2996,36 +2996,36 @@
         <v>19.381</v>
       </c>
       <c r="AQ11" t="n">
-        <v>118.556</v>
+        <v>0</v>
       </c>
       <c r="AR11" t="n">
         <v>6.201</v>
       </c>
       <c r="AS11" t="n">
-        <v>143.76</v>
+        <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>135.407</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>110.214</v>
+        <v>0</v>
       </c>
       <c r="AV11" t="n">
-        <v>22.262</v>
+        <v>0</v>
       </c>
       <c r="AW11" t="n">
-        <v>16.205</v>
+        <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>16.721</v>
+        <v>0</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>0.585</v>
+        <v>0</v>
       </c>
       <c r="BA11" t="n">
         <v>1.066</v>
@@ -3040,36 +3040,36 @@
         <v>18.396</v>
       </c>
       <c r="BE11" t="n">
-        <v>120.906</v>
+        <v>0</v>
       </c>
       <c r="BF11" t="n">
         <v>6.138</v>
       </c>
       <c r="BG11" t="n">
-        <v>144.601</v>
+        <v>0</v>
       </c>
       <c r="BH11" t="n">
-        <v>132.57</v>
+        <v>0</v>
       </c>
       <c r="BI11" t="n">
-        <v>108.028</v>
+        <v>0</v>
       </c>
       <c r="BJ11" t="n">
-        <v>24.781</v>
+        <v>0</v>
       </c>
       <c r="BK11" t="n">
-        <v>17.099</v>
+        <v>0</v>
       </c>
       <c r="BL11" t="n">
-        <v>17.549</v>
+        <v>0</v>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="BN11" t="n">
-        <v>0.601</v>
+        <v>0</v>
       </c>
       <c r="BO11" t="n">
         <v>1.05</v>
@@ -3084,7 +3084,7 @@
         <v>19.809</v>
       </c>
       <c r="BS11" t="n">
-        <v>122.402</v>
+        <v>0</v>
       </c>
       <c r="BT11" t="n">
         <v>6.269</v>
@@ -3100,30 +3100,30 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>142.14</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>128.108</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>105.668</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>25.716</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>17.718</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>17.086</v>
+        <v>0</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>0.608</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
         <v>1.034</v>
@@ -3138,36 +3138,36 @@
         <v>20.173</v>
       </c>
       <c r="O12" t="n">
-        <v>108.966</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
         <v>6.229</v>
       </c>
       <c r="Q12" t="n">
-        <v>130.249</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>123.105</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>103.641</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>16.295</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>13.7</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>14.916</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>0.574</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
         <v>1.053</v>
@@ -3182,36 +3182,36 @@
         <v>14.97</v>
       </c>
       <c r="AC12" t="n">
-        <v>132.55</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
         <v>5.922</v>
       </c>
       <c r="AE12" t="n">
-        <v>153.587</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>137.676</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>110.09</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>26.59</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>17.202</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>19.34</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="AL12" t="n">
-        <v>0.62</v>
+        <v>0</v>
       </c>
       <c r="AM12" t="n">
         <v>1.044</v>
@@ -3226,36 +3226,36 @@
         <v>21.044</v>
       </c>
       <c r="AQ12" t="n">
-        <v>115.565</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
         <v>6.335</v>
       </c>
       <c r="AS12" t="n">
-        <v>135.55</v>
+        <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>130.22</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>105.098</v>
+        <v>0</v>
       </c>
       <c r="AV12" t="n">
-        <v>18.891</v>
+        <v>0</v>
       </c>
       <c r="AW12" t="n">
-        <v>15.486</v>
+        <v>0</v>
       </c>
       <c r="AX12" t="n">
-        <v>16.304</v>
+        <v>0</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>0.576</v>
+        <v>0</v>
       </c>
       <c r="BA12" t="n">
         <v>1.082</v>
@@ -3270,36 +3270,36 @@
         <v>16.894</v>
       </c>
       <c r="BE12" t="n">
-        <v>119.369</v>
+        <v>0</v>
       </c>
       <c r="BF12" t="n">
         <v>6.066</v>
       </c>
       <c r="BG12" t="n">
-        <v>140.382</v>
+        <v>0</v>
       </c>
       <c r="BH12" t="n">
-        <v>129.777</v>
+        <v>0</v>
       </c>
       <c r="BI12" t="n">
-        <v>106.124</v>
+        <v>0</v>
       </c>
       <c r="BJ12" t="n">
-        <v>23.949</v>
+        <v>0</v>
       </c>
       <c r="BK12" t="n">
-        <v>16.935</v>
+        <v>0</v>
       </c>
       <c r="BL12" t="n">
-        <v>17.157</v>
+        <v>0</v>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="BN12" t="n">
-        <v>0.595</v>
+        <v>0</v>
       </c>
       <c r="BO12" t="n">
         <v>1.053</v>
@@ -3314,7 +3314,7 @@
         <v>19.347</v>
       </c>
       <c r="BS12" t="n">
-        <v>118.963</v>
+        <v>0</v>
       </c>
       <c r="BT12" t="n">
         <v>6.232</v>
@@ -3349,7 +3349,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -3393,7 +3393,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="AL13" t="n">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="AZ13" t="n">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="BN13" t="n">
@@ -3560,30 +3560,30 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>85.84399999999999</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>182.645</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>48.915</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>63.727</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>51.262</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>45.429</v>
+        <v>0</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1.355</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>2.711</v>
@@ -3598,36 +3598,36 @@
         <v>53.473</v>
       </c>
       <c r="O14" t="n">
-        <v>8759.894</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
         <v>4.316</v>
       </c>
       <c r="Q14" t="n">
-        <v>70.836</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>176.154</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>35.308</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>44.647</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>54.111</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>26.501</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
         <v>3.319</v>
@@ -3642,36 +3642,36 @@
         <v>41.753</v>
       </c>
       <c r="AC14" t="n">
-        <v>8449.906999999999</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
         <v>4.1</v>
       </c>
       <c r="AE14" t="n">
-        <v>143.664</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>154.577</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>92.747</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>42.064</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>19.571</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>34.653</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="AL14" t="n">
-        <v>0.654</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="n">
         <v>1.308</v>
@@ -3686,36 +3686,36 @@
         <v>32.096</v>
       </c>
       <c r="AQ14" t="n">
-        <v>75.923</v>
+        <v>0</v>
       </c>
       <c r="AR14" t="n">
         <v>6.528</v>
       </c>
       <c r="AS14" t="n">
-        <v>103.5</v>
+        <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>137.428</v>
+        <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>57.253</v>
+        <v>0</v>
       </c>
       <c r="AV14" t="n">
-        <v>14.993</v>
+        <v>0</v>
       </c>
       <c r="AW14" t="n">
-        <v>15.501</v>
+        <v>0</v>
       </c>
       <c r="AX14" t="n">
-        <v>13.1</v>
+        <v>0</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>0.855</v>
+        <v>0</v>
       </c>
       <c r="BA14" t="n">
         <v>1.71</v>
@@ -3730,36 +3730,36 @@
         <v>14.531</v>
       </c>
       <c r="BE14" t="n">
-        <v>82.16</v>
+        <v>0</v>
       </c>
       <c r="BF14" t="n">
         <v>5.861</v>
       </c>
       <c r="BG14" t="n">
-        <v>100.961</v>
+        <v>0</v>
       </c>
       <c r="BH14" t="n">
-        <v>162.701</v>
+        <v>0</v>
       </c>
       <c r="BI14" t="n">
-        <v>58.556</v>
+        <v>0</v>
       </c>
       <c r="BJ14" t="n">
-        <v>52.475</v>
+        <v>0</v>
       </c>
       <c r="BK14" t="n">
-        <v>43.193</v>
+        <v>0</v>
       </c>
       <c r="BL14" t="n">
-        <v>38.544</v>
+        <v>0</v>
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="BN14" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="BO14" t="n">
         <v>2.04</v>
@@ -3774,7 +3774,7 @@
         <v>44.738</v>
       </c>
       <c r="BS14" t="n">
-        <v>4340.768</v>
+        <v>0</v>
       </c>
       <c r="BT14" t="n">
         <v>5.749</v>
